--- a/Resultados.xlsx
+++ b/Resultados.xlsx
@@ -3001,6 +3001,7 @@
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -3305,10 +3306,10 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C28" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.3329718841651612E-2</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -3316,10 +3317,10 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C29" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.3817130436414402E-2</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -3327,10 +3328,10 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C30" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.4304776476154331E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -3338,10 +3339,10 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C31" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.4792657073639361E-2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -3349,10 +3350,10 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C32" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.5280772341691744E-2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -3360,10 +3361,10 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C33" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.5769122393188013E-2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -3371,10 +3372,10 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C34" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.6257707341059132E-2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -3382,10 +3383,10 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C35" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.6746527298290202E-2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -3393,10 +3394,10 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C36" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.7235582377920621E-2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -3404,10 +3405,10 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C37" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.7724872693044347E-2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -3415,10 +3416,10 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C38" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.8214398356809623E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -3426,10 +3427,10 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C39" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.8704159482419273E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -3437,10 +3438,10 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C40" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.9194156183130247E-2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -3448,10 +3449,10 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C41" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>1.968438857225422E-2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -3459,10 +3460,10 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C42" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.0174856763157435E-2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -3470,10 +3471,10 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C43" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.0665560869260417E-2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -3481,10 +3482,10 @@
         <v>44</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C44" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.1156501004038545E-2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -3492,10 +3493,10 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C45" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.1647677281021488E-2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -3503,10 +3504,10 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C46" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.2139089813793617E-2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -3514,10 +3515,10 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C47" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.2630738715994029E-2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -3525,10 +3526,10 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C48" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.3122624101316377E-2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -3536,10 +3537,10 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C49" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.3614746083509032E-2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -3547,10 +3548,10 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C50" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.4107104776375222E-2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -3558,10 +3559,10 @@
         <v>51</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C51" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.4599700293772599E-2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -3569,10 +3570,10 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C52" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.5092532749613809E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -3580,10 +3581,10 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C53" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.5585602257866356E-2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -3591,10 +3592,10 @@
         <v>54</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C54" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.6078908932552311E-2</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -3602,10 +3603,10 @@
         <v>55</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C55" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.6572452887748881E-2</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -3613,10 +3614,10 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C56" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.706623423758785E-2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -3624,10 +3625,10 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C57" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.7560253096256135E-2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -3635,10 +3636,10 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C58" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.8054509577995362E-2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -3646,10 +3647,10 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C59" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.8549003797102301E-2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -3657,10 +3658,10 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C60" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.9043735867928716E-2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -3668,10 +3669,10 @@
         <v>61</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C61" s="2">
-        <v>1.284254157915214E-2</v>
+        <v>2.9538705904881085E-2</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -3682,7 +3683,7 @@
         <v>-1.0985093450605679E-3</v>
       </c>
       <c r="C62" s="2">
-        <v>1.1729924582152478E-2</v>
+        <v>2.8407748015342946E-2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -3693,7 +3694,7 @@
         <v>-8.1142753177588026E-4</v>
       </c>
       <c r="C63" s="2">
-        <v>1.090897906662505E-2</v>
+        <v>2.757326965471165E-2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -3704,7 +3705,7 @@
         <v>1.9262603681734599E-4</v>
       </c>
       <c r="C64" s="2">
-        <v>1.1103706456845686E-2</v>
+        <v>2.7771207021184522E-2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -3715,7 +3716,7 @@
         <v>1.4532620082012681E-3</v>
       </c>
       <c r="C65" s="2">
-        <v>1.2573105059790918E-2</v>
+        <v>2.9264827869471616E-2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -3726,7 +3727,7 @@
         <v>1.9573283391289909E-3</v>
       </c>
       <c r="C66" s="2">
-        <v>1.4555043093764226E-2</v>
+        <v>3.1279437085529195E-2</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -3737,7 +3738,7 @@
         <v>-5.59862120625168E-4</v>
       </c>
       <c r="C67" s="2">
-        <v>1.3987032155846749E-2</v>
+        <v>3.0702062792925346E-2</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -3748,7 +3749,7 @@
         <v>-2.0311426252934582E-3</v>
       </c>
       <c r="C68" s="2">
-        <v>1.1927479873340162E-2</v>
+        <v>2.8608559899208786E-2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -3759,7 +3760,7 @@
         <v>1.7519779269955381E-3</v>
       </c>
       <c r="C69" s="2">
-        <v>1.3700354481798342E-2</v>
+        <v>3.0410659391670834E-2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -3770,7 +3771,7 @@
         <v>-9.2110047006506348E-3</v>
       </c>
       <c r="C70" s="2">
-        <v>4.3631557516152948E-3</v>
+        <v>2.0919541964413639E-2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -3781,7 +3782,7 @@
         <v>-8.8666403020151649E-3</v>
       </c>
       <c r="C71" s="2">
-        <v>-4.5421710830311213E-3</v>
+        <v>1.1867415608517149E-2</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -3792,7 +3793,7 @@
         <v>1.714430777890862E-3</v>
       </c>
       <c r="C72" s="2">
-        <v>-2.8355275430433837E-3</v>
+        <v>1.360219224898131E-2</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -3803,7 +3804,7 @@
         <v>3.7206658793950639E-3</v>
       </c>
       <c r="C73" s="2">
-        <v>8.7458828577226201E-4</v>
+        <v>1.7373467340962206E-2</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -3814,7 +3815,7 @@
         <v>-1.587066673418183E-3</v>
       </c>
       <c r="C74" s="2">
-        <v>-7.1386641756731705E-4</v>
+        <v>1.5758827816525382E-2</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -3825,7 +3826,7 @@
         <v>1.5756254649254089E-3</v>
       </c>
       <c r="C75" s="2">
-        <v>8.6063426125207346E-4</v>
+        <v>1.7359283291855973E-2</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -3836,7 +3837,7 @@
         <v>-1.663933742466297E-3</v>
       </c>
       <c r="C76" s="2">
-        <v>-8.0473151960148927E-4</v>
+        <v>1.5666464852175325E-2</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -3847,7 +3848,7 @@
         <v>1.092539574589337E-4</v>
       </c>
       <c r="C77" s="2">
-        <v>-6.9556548224568358E-4</v>
+        <v>1.5777430432918748E-2</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -3858,7 +3859,7 @@
         <v>7.6431421858763149E-4</v>
       </c>
       <c r="C78" s="2">
-        <v>6.8217105753802797E-5</v>
+        <v>1.6553803565919054E-2</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -3869,7 +3870,7 @@
         <v>-1.3506845622993501E-3</v>
       </c>
       <c r="C79" s="2">
-        <v>-1.2825595963371938E-3</v>
+        <v>1.5180760036695915E-2</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -3880,7 +3881,7 @@
         <v>6.5790924683824447E-3</v>
       </c>
       <c r="C80" s="2">
-        <v>5.2880947938646729E-3</v>
+        <v>2.185972812910009E-2</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -3891,7 +3892,7 @@
         <v>-1.66156917387785E-4</v>
       </c>
       <c r="C81" s="2">
-        <v>5.1210592229470817E-3</v>
+        <v>2.1689939066671542E-2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -3902,7 +3903,7 @@
         <v>7.3468043607330712E-3</v>
       </c>
       <c r="C82" s="2">
-        <v>1.2505487003910788E-2</v>
+        <v>2.919609516632363E-2</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -3913,7 +3914,7 @@
         <v>-2.3342705553974579E-3</v>
       </c>
       <c r="C83" s="2">
-        <v>1.0142025258419238E-2</v>
+        <v>2.6793673025646853E-2</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -3924,7 +3925,7 @@
         <v>7.5413483958974327E-5</v>
       </c>
       <c r="C84" s="2">
-        <v>1.0218203587837281E-2</v>
+        <v>2.6871107113836671E-2</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -3935,7 +3936,7 @@
         <v>-6.127350732412125E-3</v>
       </c>
       <c r="C85" s="2">
-        <v>4.0282423381873397E-3</v>
+        <v>2.0579107683569901E-2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -3946,7 +3947,7 @@
         <v>-2.781805157286607E-3</v>
       </c>
       <c r="C86" s="2">
-        <v>1.2352313955895512E-3</v>
+        <v>1.7740055458396711E-2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -3957,7 +3958,7 @@
         <v>3.1041504734398781E-4</v>
       </c>
       <c r="C87" s="2">
-        <v>1.5460298773457737E-3</v>
+        <v>1.8055977285895749E-2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -3968,7 +3969,7 @@
         <v>-9.7858329970803778E-3</v>
       </c>
       <c r="C88" s="2">
-        <v>-8.2549323099227936E-3</v>
+        <v>8.0934515104965493E-3</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -3979,7 +3980,7 @@
         <v>7.5179290703263901E-3</v>
       </c>
       <c r="C89" s="2">
-        <v>-7.9906323518272868E-4</v>
+        <v>1.5672226575212989E-2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -3990,7 +3991,7 @@
         <v>5.7667072638857703E-3</v>
       </c>
       <c r="C90" s="2">
-        <v>4.9630360649405248E-3</v>
+        <v>2.1529310981931359E-2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -4001,7 +4002,7 @@
         <v>2.24900470474113E-2</v>
       </c>
       <c r="C91" s="2">
-        <v>2.7564702026950272E-2</v>
+        <v>4.45035532462245E-2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -4012,7 +4013,7 @@
         <v>5.5353056933051831E-3</v>
       </c>
       <c r="C92" s="2">
-        <v>3.3252586772319431E-2</v>
+        <v>5.0285199711185842E-2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -4023,7 +4024,7 @@
         <v>3.3318034952741089E-6</v>
       </c>
       <c r="C93" s="2">
-        <v>3.3256029366899614E-2</v>
+        <v>5.028869905508529E-2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -4034,7 +4035,7 @@
         <v>1.17557043789634E-3</v>
       </c>
       <c r="C94" s="2">
-        <v>3.4470694609801594E-2</v>
+        <v>5.1523387400951179E-2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -4045,7 +4046,7 @@
         <v>1.4651882858821891E-3</v>
       </c>
       <c r="C95" s="2">
-        <v>3.5986388953632369E-2</v>
+        <v>5.3064067150502298E-2</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -4056,7 +4057,7 @@
         <v>2.115082841348934E-3</v>
       </c>
       <c r="C96" s="2">
-        <v>3.8177585988779301E-2</v>
+        <v>5.5291384889773525E-2</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -4067,7 +4068,7 @@
         <v>2.8955722213039161E-3</v>
       </c>
       <c r="C97" s="2">
-        <v>4.1183704167548851E-2</v>
+        <v>5.8347057309241702E-2</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -4078,7 +4079,7 @@
         <v>5.4121177284942746E-3</v>
       </c>
       <c r="C98" s="2">
-        <v>4.6818712951493355E-2</v>
+        <v>6.4074956181004838E-2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -4089,7 +4090,7 @@
         <v>1.08368148514793E-3</v>
       </c>
       <c r="C99" s="2">
-        <v>4.7953131009025325E-2</v>
+        <v>6.5228074509827969E-2</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -4100,7 +4101,7 @@
         <v>-1.111111111111111E-4</v>
       </c>
       <c r="C100" s="2">
-        <v>4.783669177224667E-2</v>
+        <v>6.5109715834882426E-2</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -4108,10 +4109,10 @@
         <v>101</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C101" s="2">
-        <v>4.783669177224667E-2</v>
+        <v>6.5622033608198932E-2</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -4122,7 +4123,7 @@
         <v>-4.3258791899390362E-3</v>
       </c>
       <c r="C102" s="2">
-        <v>4.3303876832854658E-2</v>
+        <v>6.101228142867271E-2</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -4133,7 +4134,7 @@
         <v>-1.9966247426437471E-3</v>
       </c>
       <c r="C103" s="2">
-        <v>4.1220790498274054E-2</v>
+        <v>5.8893838055323326E-2</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -4144,7 +4145,7 @@
         <v>2.1747394317646451E-4</v>
       </c>
       <c r="C104" s="2">
-        <v>4.1447228889300899E-2</v>
+        <v>5.9124119873690401E-2</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -4155,7 +4156,7 @@
         <v>1.537963405247228E-3</v>
       </c>
       <c r="C105" s="2">
-        <v>4.3048936615828808E-2</v>
+        <v>6.0753014011670811E-2</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -4166,7 +4167,7 @@
         <v>-9.8899339791438728E-4</v>
       </c>
       <c r="C106" s="2">
-        <v>4.2017368103814193E-2</v>
+        <v>5.9703936283995486E-2</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -4177,7 +4178,7 @@
         <v>1.845381209006936E-4</v>
       </c>
       <c r="C107" s="2">
-        <v>4.2209660030869997E-2</v>
+        <v>5.9899492057108435E-2</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
@@ -4188,7 +4189,7 @@
         <v>-1.203574233102173E-3</v>
       </c>
       <c r="C108" s="2">
-        <v>4.0955283338566774E-2</v>
+        <v>5.8623824338790487E-2</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -4199,7 +4200,7 @@
         <v>-3.234595095700708E-3</v>
       </c>
       <c r="C109" s="2">
-        <v>3.7588214484236174E-2</v>
+        <v>5.5199604908392388E-2</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -4210,7 +4211,7 @@
         <v>-6.9028746558793728E-4</v>
       </c>
       <c r="C110" s="2">
-        <v>3.6871980345335939E-2</v>
+        <v>5.4471213847430706E-2</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -4221,7 +4222,7 @@
         <v>-4.5575014838591084E-3</v>
       </c>
       <c r="C111" s="2">
-        <v>3.2146434756340055E-2</v>
+        <v>4.9665459725634235E-2</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -4232,7 +4233,7 @@
         <v>-4.3860309586631991E-3</v>
       </c>
       <c r="C112" s="2">
-        <v>2.7619408539624857E-2</v>
+        <v>4.5061594523038193E-2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -4243,7 +4244,7 @@
         <v>-5.2544484559651668E-3</v>
       </c>
       <c r="C113" s="2">
-        <v>2.2219835325104072E-2</v>
+        <v>3.9570372241308147E-2</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -4254,7 +4255,7 @@
         <v>-2.8317665852527051E-3</v>
       </c>
       <c r="C114" s="2">
-        <v>1.9325147352647887E-2</v>
+        <v>3.662655159817646E-2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -4265,7 +4266,7 @@
         <v>1.2523766410044929E-3</v>
       </c>
       <c r="C115" s="2">
-        <v>2.0601726356780717E-2</v>
+        <v>3.7924798476842908E-2</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -4276,7 +4277,7 @@
         <v>-1.9209614826375611E-3</v>
       </c>
       <c r="C116" s="2">
-        <v>1.864118975133593E-2</v>
+        <v>3.5930984917094545E-2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -4287,7 +4288,7 @@
         <v>-1.89548736202518E-3</v>
       </c>
       <c r="C117" s="2">
-        <v>1.671036824972404E-2</v>
+        <v>3.396739082725389E-2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -4298,7 +4299,7 @@
         <v>1.1016690626542491E-2</v>
       </c>
       <c r="C118" s="2">
-        <v>2.7911151833529432E-2</v>
+        <v>4.5358289689931157E-2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -4309,7 +4310,7 @@
         <v>6.3494966124963423E-3</v>
       </c>
       <c r="C119" s="2">
-        <v>3.4437870210043686E-2</v>
+        <v>5.1995788609162333E-2</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -4320,7 +4321,7 @@
         <v>1.505282132757631E-3</v>
       </c>
       <c r="C120" s="2">
-        <v>3.5994991053518818E-2</v>
+        <v>5.3579339073492063E-2</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -4331,7 +4332,7 @@
         <v>5.0400613313613838E-4</v>
       </c>
       <c r="C121" s="2">
-        <v>3.6517138882908001E-2</v>
+        <v>5.4110349522130577E-2</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -4342,7 +4343,7 @@
         <v>1.1179912214187701E-2</v>
       </c>
       <c r="C122" s="2">
-        <v>4.8105309504120015E-2</v>
+        <v>6.589521069385483E-2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -4353,7 +4354,7 @@
         <v>-9.4305108918298301E-3</v>
       </c>
       <c r="C123" s="2">
-        <v>3.8221140967056755E-2</v>
+        <v>5.58432742998572E-2</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -4364,7 +4365,7 @@
         <v>-4.2492709556730436E-3</v>
       </c>
       <c r="C124" s="2">
-        <v>3.3809458027179745E-2</v>
+        <v>5.1356710140632061E-2</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -4375,7 +4376,7 @@
         <v>1.2422740085903361E-2</v>
       </c>
       <c r="C125" s="2">
-        <v>4.6652204222600059E-2</v>
+        <v>6.4417441288279628E-2</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -4386,7 +4387,7 @@
         <v>-1.8873085384329589E-3</v>
       </c>
       <c r="C126" s="2">
-        <v>4.4676848580801051E-2</v>
+        <v>6.2408557162879248E-2</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -4397,7 +4398,7 @@
         <v>-2.033436188251656E-3</v>
       </c>
       <c r="C127" s="2">
-        <v>4.2552564871868127E-2</v>
+        <v>6.0248217156035934E-2</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -4408,7 +4409,7 @@
         <v>2.020686065407873E-3</v>
       </c>
       <c r="C128" s="2">
-        <v>4.4659236312160004E-2</v>
+        <v>6.2390645954316711E-2</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
@@ -4419,7 +4420,7 @@
         <v>-1.0522180311659349E-4</v>
       </c>
       <c r="C129" s="2">
-        <v>4.4549315383672905E-2</v>
+        <v>6.2278859294935242E-2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -4430,7 +4431,7 @@
         <v>1.57682203646216E-3</v>
       </c>
       <c r="C130" s="2">
-        <v>4.6196383762341496E-2</v>
+        <v>6.3953884009139442E-2</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -4441,7 +4442,7 @@
         <v>-2.0924315459000969E-3</v>
       </c>
       <c r="C131" s="2">
-        <v>4.4007289445750504E-2</v>
+        <v>6.1727633338855836E-2</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -4452,7 +4453,7 @@
         <v>2.5260973044992341E-3</v>
       </c>
       <c r="C132" s="2">
-        <v>4.6644553445496936E-2</v>
+        <v>6.4409660651545408E-2</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -4463,7 +4464,7 @@
         <v>5.2417151774638987E-3</v>
       </c>
       <c r="C133" s="2">
-        <v>5.213076608670221E-2</v>
+        <v>6.9988992924821927E-2</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
@@ -4474,7 +4475,7 @@
         <v>-4.6447638975682872E-4</v>
       </c>
       <c r="C134" s="2">
-        <v>5.1642076186918191E-2</v>
+        <v>6.9492008300308758E-2</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -4485,7 +4486,7 @@
         <v>-1.919338088120067E-3</v>
       </c>
       <c r="C135" s="2">
-        <v>4.9623619495022947E-2</v>
+        <v>6.743929155383796E-2</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -4496,7 +4497,7 @@
         <v>1.0270268836453441E-3</v>
       </c>
       <c r="C136" s="2">
-        <v>5.070161116995351E-2</v>
+        <v>6.8535580402923124E-2</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -4507,7 +4508,7 @@
         <v>5.5084376352697263E-3</v>
       </c>
       <c r="C137" s="2">
-        <v>5.6489335468360477E-2</v>
+        <v>7.4421542008639249E-2</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -4518,7 +4519,7 @@
         <v>4.4194963128765322E-3</v>
       </c>
       <c r="C138" s="2">
-        <v>6.1158486191056197E-2</v>
+        <v>7.9169944052021601E-2</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -4529,7 +4530,7 @@
         <v>-2.1737444498231332E-3</v>
       </c>
       <c r="C139" s="2">
-        <v>5.8851798821315665E-2</v>
+        <v>7.6824104375722582E-2</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -4540,7 +4541,7 @@
         <v>-3.5388609296950948E-3</v>
       </c>
       <c r="C140" s="2">
-        <v>5.5104669560129479E-2</v>
+        <v>7.3013373624593356E-2</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
@@ -4551,7 +4552,7 @@
         <v>5.9496504629715768E-3</v>
       </c>
       <c r="C141" s="2">
-        <v>6.138217354586132E-2</v>
+        <v>7.9397428139753423E-2</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -4562,7 +4563,7 @@
         <v>4.008222372754118E-3</v>
       </c>
       <c r="C142" s="2">
-        <v>6.56364293199104E-2</v>
+        <v>8.3723893060316495E-2</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
@@ -4573,7 +4574,7 @@
         <v>-2.0000000000000001E-4</v>
       </c>
       <c r="C143" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.3507148281704385E-2</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
@@ -4581,10 +4582,10 @@
         <v>144</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C144" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.4028315220027849E-2</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -4592,10 +4593,10 @@
         <v>145</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C145" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.4549732839648617E-2</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -4603,10 +4604,10 @@
         <v>146</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C146" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.50714012611445E-2</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
@@ -4614,10 +4615,10 @@
         <v>147</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C147" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.5593320605151041E-2</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
@@ -4625,10 +4626,10 @@
         <v>148</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C148" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.6115490992362001E-2</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
@@ -4636,10 +4637,10 @@
         <v>149</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C149" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.6637912543529302E-2</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
@@ -4647,10 +4648,10 @@
         <v>150</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C150" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.7160585379462668E-2</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
@@ -4658,10 +4659,10 @@
         <v>151</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C151" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.7683509621030137E-2</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
@@ -4669,10 +4670,10 @@
         <v>152</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C152" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.8206685389157824E-2</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
@@ -4680,10 +4681,10 @@
         <v>153</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C153" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.873011280482998E-2</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
@@ -4691,10 +4692,10 @@
         <v>154</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C154" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.925379198908899E-2</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
@@ -4702,10 +4703,10 @@
         <v>155</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C155" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>8.9777723063035636E-2</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
@@ -4713,10 +4714,10 @@
         <v>156</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C156" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>9.0301906147828959E-2</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
@@ -4724,10 +4725,10 @@
         <v>157</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C157" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>9.0826341364685981E-2</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
@@ -4735,10 +4736,10 @@
         <v>158</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C158" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>9.1351028834882303E-2</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -4746,10 +4747,10 @@
         <v>159</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C159" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>9.1875968679751882E-2</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -4757,10 +4758,10 @@
         <v>160</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C160" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>9.2401161020686823E-2</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
@@ -4768,10 +4769,10 @@
         <v>161</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C161" s="2">
-        <v>6.5423302034046463E-2</v>
+        <v>9.2926605979137655E-2</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
@@ -4782,7 +4783,7 @@
         <v>-3.7929180045143309E-3</v>
       </c>
       <c r="C162" s="2">
-        <v>6.1382238809332391E-2</v>
+        <v>8.8781224977706616E-2</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -4793,7 +4794,7 @@
         <v>-1.1060320550857431E-3</v>
       </c>
       <c r="C163" s="2">
-        <v>6.0208316030510647E-2</v>
+        <v>8.7576998041905801E-2</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
@@ -4804,7 +4805,7 @@
         <v>6.8227592163201624E-4</v>
       </c>
       <c r="C164" s="2">
-        <v>6.0931670636452398E-2</v>
+        <v>8.8319025640590632E-2</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
@@ -4815,7 +4816,7 @@
         <v>5.5495037416599504E-3</v>
       </c>
       <c r="C165" s="2">
-        <v>6.6819314912294911E-2</v>
+        <v>9.4358656145502803E-2</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -4826,7 +4827,7 @@
         <v>-6.127778772554421E-3</v>
       </c>
       <c r="C166" s="2">
-        <v>6.0282082160224348E-2</v>
+        <v>8.7652668402813133E-2</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -4837,7 +4838,7 @@
         <v>-1.7452384764039129E-3</v>
       </c>
       <c r="C167" s="2">
-        <v>5.8431637074596664E-2</v>
+        <v>8.5754455116953066E-2</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -4848,7 +4849,7 @@
         <v>2.5852065633180771E-3</v>
       </c>
       <c r="C168" s="2">
-        <v>6.1167901489585431E-2</v>
+        <v>8.8561354660473199E-2</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -4859,7 +4860,7 @@
         <v>-6.7885720899832878E-4</v>
       </c>
       <c r="C169" s="2">
-        <v>6.0447520009701633E-2</v>
+        <v>8.782237693742502E-2</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -4870,7 +4871,7 @@
         <v>-1.993751528444586E-3</v>
       </c>
       <c r="C170" s="2">
-        <v>5.8333251145846955E-2</v>
+        <v>8.5653529410729734E-2</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -4881,7 +4882,7 @@
         <v>7.9124201140865456E-3</v>
       </c>
       <c r="C171" s="2">
-        <v>6.6707228449620001E-2</v>
+        <v>9.4243676233768239E-2</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
@@ -4892,7 +4893,7 @@
         <v>-1.0543860475489769E-3</v>
       </c>
       <c r="C172" s="2">
-        <v>6.5582507231123091E-2</v>
+        <v>9.3089920968928652E-2</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
@@ -4903,7 +4904,7 @@
         <v>1.0585803929458279E-3</v>
       </c>
       <c r="C173" s="2">
-        <v>6.6710511980344056E-2</v>
+        <v>9.4247044526993159E-2</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
@@ -4914,7 +4915,7 @@
         <v>6.0708869313108507E-3</v>
       </c>
       <c r="C174" s="2">
-        <v>7.3186390887017436E-2</v>
+        <v>0.10089009460923762</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
@@ -4925,7 +4926,7 @@
         <v>-6.324093696042336E-3</v>
       </c>
       <c r="C175" s="2">
-        <v>6.6399459597730442E-2</v>
+        <v>9.392796250188383E-2</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
@@ -4936,7 +4937,7 @@
         <v>1.40919738831501E-3</v>
       </c>
       <c r="C176" s="2">
-        <v>6.7902226931096127E-2</v>
+        <v>9.5469522929646194E-2</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
@@ -4947,7 +4948,7 @@
         <v>1.3304763067529859E-2</v>
       </c>
       <c r="C177" s="2">
-        <v>8.2110413039701763E-2</v>
+        <v>0.11004448537992502</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
@@ -4958,7 +4959,7 @@
         <v>-6.3991840375868178E-3</v>
       </c>
       <c r="C178" s="2">
-        <v>7.5185789357671673E-2</v>
+        <v>0.10294110642807056</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
@@ -4969,7 +4970,7 @@
         <v>-2.0000000000000001E-4</v>
       </c>
       <c r="C179" s="2">
-        <v>7.4970752199800192E-2</v>
+        <v>0.10272051820678499</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
@@ -4980,7 +4981,7 @@
         <v>-3.9825113656985194E-3</v>
       </c>
       <c r="C180" s="2">
-        <v>7.068966896137098E-2</v>
+        <v>9.8328921209837578E-2</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -4991,7 +4992,7 @@
         <v>-2.3741536251292222E-3</v>
       </c>
       <c r="C181" s="2">
-        <v>6.8147687202417873E-2</v>
+        <v>9.5721319619962913E-2</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
@@ -5002,7 +5003,7 @@
         <v>-7.5700268762392987E-3</v>
       </c>
       <c r="C182" s="2">
-        <v>6.0061780502502701E-2</v>
+        <v>8.742667978157144E-2</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
@@ -5013,7 +5014,7 @@
         <v>5.3316970082274168E-3</v>
       </c>
       <c r="C183" s="2">
-        <v>6.5713708726144085E-2</v>
+        <v>9.3224509356829369E-2</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
@@ -5024,7 +5025,7 @@
         <v>4.5914505026184316E-3</v>
       </c>
       <c r="C184" s="2">
-        <v>7.0606880469722022E-2</v>
+        <v>9.8243995579790494E-2</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
@@ -5035,7 +5036,7 @@
         <v>5.2749025732978403E-3</v>
       </c>
       <c r="C185" s="2">
-        <v>7.6254227458502161E-2</v>
+        <v>0.10403712565818324</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
@@ -5046,7 +5047,7 @@
         <v>3.492465782876316E-3</v>
       </c>
       <c r="C186" s="2">
-        <v>8.0013008521576973E-2</v>
+        <v>0.10789293754256959</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
@@ -5057,7 +5058,7 @@
         <v>7.9213871007473499E-3</v>
       </c>
       <c r="C187" s="2">
-        <v>8.8568209635919146E-2</v>
+        <v>0.1166689863670284</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
@@ -5068,7 +5069,7 @@
         <v>-5.3921966416329622E-3</v>
       </c>
       <c r="C188" s="2">
-        <v>8.2698435791731986E-2</v>
+        <v>0.11064768760892449</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
@@ -5079,7 +5080,7 @@
         <v>1.0748947524455001E-3</v>
       </c>
       <c r="C189" s="2">
-        <v>8.3862222658845409E-2</v>
+        <v>0.111841516980151</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
@@ -5090,7 +5091,7 @@
         <v>-1.016403351357594E-3</v>
       </c>
       <c r="C190" s="2">
-        <v>8.276058146332517E-2</v>
+        <v>0.11071143753611395</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
@@ -5101,7 +5102,7 @@
         <v>1.0681744463338599E-3</v>
       </c>
       <c r="C191" s="2">
-        <v>8.3917158647941928E-2</v>
+        <v>0.11189787111094077</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
@@ -5112,7 +5113,7 @@
         <v>-4.9136798127123824E-3</v>
       </c>
       <c r="C192" s="2">
-        <v>7.8591136786840959E-2</v>
+        <v>0.10643436098786509</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
@@ -5123,7 +5124,7 @@
         <v>-2.685350303248674E-3</v>
       </c>
       <c r="C193" s="2">
-        <v>7.5694741750589142E-2</v>
+        <v>0.10346319714106159</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
@@ -5134,7 +5135,7 @@
         <v>1.8527721237622339E-2</v>
       </c>
       <c r="C194" s="2">
-        <v>9.5624914062520078E-2</v>
+        <v>0.12390785565366656</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
@@ -5145,7 +5146,7 @@
         <v>1.718630892139539E-3</v>
       </c>
       <c r="C195" s="2">
-        <v>9.7507888886025573E-2</v>
+        <v>0.12583943841431122</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
@@ -5156,7 +5157,7 @@
         <v>8.9833397068119424E-4</v>
       </c>
       <c r="C196" s="2">
-        <v>9.849381750570245E-2</v>
+        <v>0.12685081822737146</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
@@ -5167,7 +5168,7 @@
         <v>-2.0000000000000001E-4</v>
       </c>
       <c r="C197" s="2">
-        <v>9.8274118742201322E-2</v>
+        <v>0.12662544806372608</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
@@ -5175,10 +5176,10 @@
         <v>198</v>
       </c>
       <c r="B198">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C198" s="2">
-        <v>9.8274118742201322E-2</v>
+        <v>0.12716735490424469</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
@@ -5186,10 +5187,10 @@
         <v>199</v>
       </c>
       <c r="B199">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C199" s="2">
-        <v>9.8274118742201322E-2</v>
+        <v>0.12770952240195357</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
@@ -5197,10 +5198,10 @@
         <v>200</v>
       </c>
       <c r="B200">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C200" s="2">
-        <v>9.8274118742201322E-2</v>
+        <v>0.12825195068222883</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
@@ -5208,10 +5209,10 @@
         <v>201</v>
       </c>
       <c r="B201">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C201" s="2">
-        <v>9.8274118742201322E-2</v>
+        <v>0.12879463987050699</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -5219,10 +5220,10 @@
         <v>202</v>
       </c>
       <c r="B202">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C202" s="2">
-        <v>9.8274118742201322E-2</v>
+        <v>0.12933759009228468</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
@@ -5230,10 +5231,10 @@
         <v>203</v>
       </c>
       <c r="B203">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C203" s="2">
-        <v>9.8274118742201322E-2</v>
+        <v>0.12988080147311906</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
@@ -5241,10 +5242,10 @@
         <v>204</v>
       </c>
       <c r="B204">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C204" s="2">
-        <v>9.8274118742201322E-2</v>
+        <v>0.13042427413862753</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
@@ -5255,7 +5256,7 @@
         <v>4.9996995876242531E-4</v>
       </c>
       <c r="C205" s="2">
-        <v>9.8823222808058664E-2</v>
+        <v>0.1309894523163527</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
@@ -5266,7 +5267,7 @@
         <v>5.0529846362673807E-3</v>
       </c>
       <c r="C206" s="2">
-        <v>0.10437555967088173</v>
+        <v>0.13670432464268786</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
@@ -5277,7 +5278,7 @@
         <v>-1.025220036193113E-3</v>
       </c>
       <c r="C207" s="2">
-        <v>0.10324333171962521</v>
+        <v>0.1355389525938368</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
@@ -5288,7 +5289,7 @@
         <v>8.3872341933867046E-3</v>
       </c>
       <c r="C208" s="2">
-        <v>0.11249649191504986</v>
+        <v>0.14506298372495421</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
@@ -5299,7 +5300,7 @@
         <v>-2.864446725193052E-3</v>
       </c>
       <c r="C209" s="2">
-        <v>0.10930980498199502</v>
+        <v>0.14178301181108352</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
@@ -5310,7 +5311,7 @@
         <v>3.4280266775348561E-4</v>
       </c>
       <c r="C210" s="2">
-        <v>0.10969007934250798</v>
+        <v>0.14217441807352799</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
@@ -5321,7 +5322,7 @@
         <v>3.4336061784294028E-3</v>
       </c>
       <c r="C211" s="2">
-        <v>0.11350031805508025</v>
+        <v>0.14609619521226933</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
@@ -5332,7 +5333,7 @@
         <v>1.730946707258372E-3</v>
       </c>
       <c r="C212" s="2">
-        <v>0.11542772776414878</v>
+        <v>0.14808002664757339</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
@@ -5343,7 +5344,7 @@
         <v>-4.2462993758769882E-4</v>
       </c>
       <c r="C213" s="2">
-        <v>0.1149540837577247</v>
+        <v>0.14759251749751229</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
@@ -5354,7 +5355,7 @@
         <v>-9.9600745173456136E-4</v>
       </c>
       <c r="C214" s="2">
-        <v>0.1138435811819602</v>
+        <v>0.14644950679852997</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
@@ -5365,7 +5366,7 @@
         <v>-1.7460332331317361E-4</v>
       </c>
       <c r="C215" s="2">
-        <v>0.11364910039103478</v>
+        <v>0.14624933290463218</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
@@ -5376,7 +5377,7 @@
         <v>8.0917619215539888E-3</v>
       </c>
       <c r="C216" s="2">
-        <v>0.12266048377555179</v>
+        <v>0.1555245096092365</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
@@ -5387,7 +5388,7 @@
         <v>-4.8808705149637893E-3</v>
       </c>
       <c r="C217" s="2">
-        <v>0.1171809233219767</v>
+        <v>0.1498845441009668</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
@@ -5398,7 +5399,7 @@
         <v>-2.0000000000000001E-4</v>
       </c>
       <c r="C218" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.14965456719214656</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
@@ -5406,10 +5407,10 @@
         <v>219</v>
       </c>
       <c r="B219">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C219" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15020755103896591</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
@@ -5417,10 +5418,10 @@
         <v>220</v>
       </c>
       <c r="B220">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C220" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15076080087101559</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
@@ -5428,10 +5429,10 @@
         <v>221</v>
       </c>
       <c r="B221">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C221" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15131431681623453</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
@@ -5439,10 +5440,10 @@
         <v>222</v>
       </c>
       <c r="B222">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C222" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15186809900262305</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
@@ -5450,10 +5451,10 @@
         <v>223</v>
       </c>
       <c r="B223">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C223" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15242214755824321</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
@@ -5461,10 +5462,10 @@
         <v>224</v>
       </c>
       <c r="B224">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C224" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15297646261121869</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
@@ -5472,10 +5473,10 @@
         <v>225</v>
       </c>
       <c r="B225">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C225" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15353104428973466</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
@@ -5483,10 +5484,10 @@
         <v>226</v>
       </c>
       <c r="B226">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C226" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15408589272203799</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
@@ -5494,10 +5495,10 @@
         <v>227</v>
       </c>
       <c r="B227">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C227" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15464100803643718</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
@@ -5505,10 +5506,10 @@
         <v>228</v>
       </c>
       <c r="B228">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C228" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15519639036130259</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
@@ -5516,10 +5517,10 @@
         <v>229</v>
       </c>
       <c r="B229">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C229" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15575203982506636</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
@@ -5527,10 +5528,10 @@
         <v>230</v>
       </c>
       <c r="B230">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C230" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15630795655622223</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
@@ -5538,10 +5539,10 @@
         <v>231</v>
       </c>
       <c r="B231">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C231" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15686414068332566</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
@@ -5549,10 +5550,10 @@
         <v>232</v>
       </c>
       <c r="B232">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C232" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15742059233499434</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
@@ -5560,10 +5561,10 @@
         <v>233</v>
       </c>
       <c r="B233">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C233" s="2">
-        <v>0.11695748713731234</v>
+        <v>0.15797731163990747</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
@@ -5574,7 +5575,7 @@
         <v>-3.8963986001456759E-3</v>
       </c>
       <c r="C234" s="2">
-        <v>0.11260537554800834</v>
+        <v>0.15346537046383332</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
@@ -5585,7 +5586,7 @@
         <v>-4.486885383683077E-3</v>
       </c>
       <c r="C235" s="2">
-        <v>0.10761324275065476</v>
+        <v>0.14828990355251462</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
@@ -5596,7 +5597,7 @@
         <v>4.3062180146482071E-5</v>
       </c>
       <c r="C236" s="2">
-        <v>0.10766093899164658</v>
+        <v>0.14833935141920165</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
@@ -5607,7 +5608,7 @@
         <v>1.293909105935691E-3</v>
       </c>
       <c r="C237" s="2">
-        <v>0.10909415156689704</v>
+        <v>0.14982519816270723</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
@@ -5618,7 +5619,7 @@
         <v>1.5524949901063059E-3</v>
       </c>
       <c r="C238" s="2">
-        <v>0.11081601468076073</v>
+        <v>0.15161029602235274</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
@@ -5629,7 +5630,7 @@
         <v>3.154766360613224E-3</v>
       </c>
       <c r="C239" s="2">
-        <v>0.11432037967670609</v>
+        <v>0.15524335744477993</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
@@ -5640,7 +5641,7 @@
         <v>2.5242217091964499E-3</v>
       </c>
       <c r="C240" s="2">
-        <v>0.11713317137008616</v>
+        <v>0.1581594478070471</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
@@ -5651,7 +5652,7 @@
         <v>-2.0092169147440191E-3</v>
       </c>
       <c r="C241" s="2">
-        <v>0.11488860850614785</v>
+        <v>0.15583245425454265</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
@@ -5662,7 +5663,7 @@
         <v>1.4789243935444309E-3</v>
       </c>
       <c r="C242" s="2">
-        <v>0.11653744446535243</v>
+        <v>0.15754184306599001</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
@@ -5673,7 +5674,7 @@
         <v>-3.096401411700539E-3</v>
       </c>
       <c r="C243" s="2">
-        <v>0.11308019634609337</v>
+        <v>0.15395762886901806</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
@@ -5684,7 +5685,7 @@
         <v>-1.0045378028575859E-2</v>
       </c>
       <c r="C244" s="2">
-        <v>0.10189888499767548</v>
+        <v>0.14236568825806969</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
@@ -5695,7 +5696,7 @@
         <v>4.2621745746698556E-3</v>
       </c>
       <c r="C245" s="2">
-        <v>0.1065953704091696</v>
+        <v>0.14723465024953838</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
@@ -5706,7 +5707,7 @@
         <v>-1.449716148798158E-3</v>
       </c>
       <c r="C246" s="2">
-        <v>0.1049911212305021</v>
+        <v>0.14557148565061084</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
@@ -5717,7 +5718,7 @@
         <v>4.3723459606249341E-4</v>
       </c>
       <c r="C247" s="2">
-        <v>0.10547426157704606</v>
+        <v>0.14607236913640009</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
@@ -5728,7 +5729,7 @@
         <v>3.9451221419756757E-3</v>
       </c>
       <c r="C248" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15059376461618668</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
@@ -5736,10 +5737,10 @@
         <v>249</v>
       </c>
       <c r="B249">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C249" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15114720021696698</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
@@ -5747,10 +5748,10 @@
         <v>250</v>
       </c>
       <c r="B250">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C250" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15170090202027126</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
@@ -5758,10 +5759,10 @@
         <v>251</v>
       </c>
       <c r="B251">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C251" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15225487015414302</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
@@ -5769,10 +5770,10 @@
         <v>252</v>
       </c>
       <c r="B252">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C252" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15280910474668716</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
@@ -5780,10 +5781,10 @@
         <v>253</v>
       </c>
       <c r="B253">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C253" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15336360592607023</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
@@ -5791,10 +5792,10 @@
         <v>254</v>
       </c>
       <c r="B254">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C254" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15391837382052059</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
@@ -5802,10 +5803,10 @@
         <v>255</v>
       </c>
       <c r="B255">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C255" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.1544734085583282</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
@@ -5813,10 +5814,10 @@
         <v>256</v>
       </c>
       <c r="B256">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C256" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15502871026784476</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
@@ -5824,10 +5825,10 @@
         <v>257</v>
       </c>
       <c r="B257">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C257" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15558427907748354</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
@@ -5835,10 +5836,10 @@
         <v>258</v>
       </c>
       <c r="B258">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C258" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15614011511571974</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
@@ -5846,10 +5847,10 @@
         <v>259</v>
       </c>
       <c r="B259">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C259" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15669621851109028</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
@@ -5857,10 +5858,10 @@
         <v>260</v>
       </c>
       <c r="B260">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C260" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.157252589392194</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
@@ -5868,10 +5869,10 @@
         <v>261</v>
       </c>
       <c r="B261">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C261" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15780922788769161</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
@@ -5879,10 +5880,10 @@
         <v>262</v>
       </c>
       <c r="B262">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C262" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15836613412630554</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
@@ -5890,10 +5891,10 @@
         <v>263</v>
       </c>
       <c r="B263">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C263" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.1589233082368203</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
@@ -5901,10 +5902,10 @@
         <v>264</v>
       </c>
       <c r="B264">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C264" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.15948075034808212</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
@@ -5912,10 +5913,10 @@
         <v>265</v>
       </c>
       <c r="B265">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C265" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16003846058899954</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
@@ -5923,10 +5924,10 @@
         <v>266</v>
       </c>
       <c r="B266">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C266" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16059643908854285</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
@@ -5934,10 +5935,10 @@
         <v>267</v>
       </c>
       <c r="B267">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C267" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16115468597574434</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
@@ -5945,10 +5946,10 @@
         <v>268</v>
       </c>
       <c r="B268">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C268" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16171320137969858</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
@@ -5956,10 +5957,10 @@
         <v>269</v>
       </c>
       <c r="B269">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C269" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16227198542956217</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
@@ -5967,10 +5968,10 @@
         <v>270</v>
       </c>
       <c r="B270">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C270" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16283103825455369</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
@@ -5978,10 +5979,10 @@
         <v>271</v>
       </c>
       <c r="B271">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C271" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16339035998395401</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
@@ -5989,10 +5990,10 @@
         <v>272</v>
       </c>
       <c r="B272">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C272" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16394995074710622</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
@@ -6000,10 +6001,10 @@
         <v>273</v>
       </c>
       <c r="B273">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C273" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16450981067341558</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
@@ -6011,10 +6012,10 @@
         <v>274</v>
       </c>
       <c r="B274">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C274" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16506993989234942</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
@@ -6022,10 +6023,10 @@
         <v>275</v>
       </c>
       <c r="B275">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C275" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16563033853343753</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
@@ -6033,10 +6034,10 @@
         <v>276</v>
       </c>
       <c r="B276">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C276" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16619100672627213</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
@@ -6044,10 +6045,10 @@
         <v>277</v>
       </c>
       <c r="B277">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C277" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16675194460050746</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
@@ -6055,10 +6056,10 @@
         <v>278</v>
       </c>
       <c r="B278">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C278" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16731315228586027</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
@@ -6066,10 +6067,10 @@
         <v>279</v>
       </c>
       <c r="B279">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C279" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16787462991210972</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
@@ -6077,10 +6078,10 @@
         <v>280</v>
       </c>
       <c r="B280">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C280" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16843637760909744</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
@@ -6088,10 +6089,10 @@
         <v>281</v>
       </c>
       <c r="B281">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C281" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16899839550672738</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
@@ -6099,10 +6100,10 @@
         <v>282</v>
       </c>
       <c r="B282">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C282" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.16956068373496605</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
@@ -6110,10 +6111,10 @@
         <v>283</v>
       </c>
       <c r="B283">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C283" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17012324242384252</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
@@ -6121,10 +6122,10 @@
         <v>284</v>
       </c>
       <c r="B284">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C284" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17068607170344832</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
@@ -6132,10 +6133,10 @@
         <v>285</v>
       </c>
       <c r="B285">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C285" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17124917170393758</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
@@ -6143,10 +6144,10 @@
         <v>286</v>
       </c>
       <c r="B286">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C286" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17181254255552716</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
@@ -6154,10 +6155,10 @@
         <v>287</v>
       </c>
       <c r="B287">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C287" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17237618438849636</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
@@ -6165,10 +6166,10 @@
         <v>288</v>
       </c>
       <c r="B288">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C288" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17294009733318716</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
@@ -6176,10 +6177,10 @@
         <v>289</v>
       </c>
       <c r="B289">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C289" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17350428152000433</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
@@ -6187,10 +6188,10 @@
         <v>290</v>
       </c>
       <c r="B290">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C290" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17406873707941542</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
@@ -6198,10 +6199,10 @@
         <v>291</v>
       </c>
       <c r="B291">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C291" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17463346414195058</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
@@ -6209,10 +6210,10 @@
         <v>292</v>
       </c>
       <c r="B292">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C292" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17519846283820287</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
@@ -6220,10 +6221,10 @@
         <v>293</v>
       </c>
       <c r="B293">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C293" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.175763733298828</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
@@ -6231,10 +6232,10 @@
         <v>294</v>
       </c>
       <c r="B294">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C294" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17632927565454465</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
@@ -6242,10 +6243,10 @@
         <v>295</v>
       </c>
       <c r="B295">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C295" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17689509003613438</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
@@ -6253,10 +6254,10 @@
         <v>296</v>
       </c>
       <c r="B296">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C296" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17746117657444174</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
@@ -6264,10 +6265,10 @@
         <v>297</v>
       </c>
       <c r="B297">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C297" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.178027535400374</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
@@ -6275,10 +6276,10 @@
         <v>298</v>
       </c>
       <c r="B298">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C298" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17859416664490155</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
@@ -6286,10 +6287,10 @@
         <v>299</v>
       </c>
       <c r="B299">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C299" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17916107043905768</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
@@ -6297,10 +6298,10 @@
         <v>300</v>
       </c>
       <c r="B300">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C300" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.17972824691393882</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
@@ -6308,10 +6309,10 @@
         <v>301</v>
       </c>
       <c r="B301">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C301" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18029569620070432</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
@@ -6319,10 +6320,10 @@
         <v>302</v>
       </c>
       <c r="B302">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C302" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18086341843057682</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
@@ -6330,10 +6331,10 @@
         <v>303</v>
       </c>
       <c r="B303">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C303" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18143141373484184</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
@@ -6341,10 +6342,10 @@
         <v>304</v>
       </c>
       <c r="B304">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C304" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18199968224484819</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
@@ -6352,10 +6353,10 @@
         <v>305</v>
       </c>
       <c r="B305">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C305" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18256822409200793</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
@@ -6363,10 +6364,10 @@
         <v>306</v>
       </c>
       <c r="B306">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C306" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18313703940779619</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
@@ -6374,10 +6375,10 @@
         <v>307</v>
       </c>
       <c r="B307">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C307" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.1837061283237513</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
@@ -6385,10 +6386,10 @@
         <v>308</v>
       </c>
       <c r="B308">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C308" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18427549097147491</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
@@ -6396,10 +6397,10 @@
         <v>309</v>
       </c>
       <c r="B309">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C309" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18484512748263213</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
@@ -6407,10 +6408,10 @@
         <v>310</v>
       </c>
       <c r="B310">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C310" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.1854150379889512</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
@@ -6418,10 +6419,10 @@
         <v>311</v>
       </c>
       <c r="B311">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C311" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18598522262222389</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
@@ -6429,10 +6430,10 @@
         <v>312</v>
       </c>
       <c r="B312">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C312" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18655568151430515</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
@@ -6440,10 +6441,10 @@
         <v>313</v>
       </c>
       <c r="B313">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C313" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18712641479711351</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
@@ -6451,10 +6452,10 @@
         <v>314</v>
       </c>
       <c r="B314">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C314" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18769742260263086</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
@@ -6462,10 +6463,10 @@
         <v>315</v>
       </c>
       <c r="B315">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C315" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18826870506290264</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
@@ -6473,10 +6474,10 @@
         <v>316</v>
       </c>
       <c r="B316">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C316" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18884026231003787</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
@@ -6484,10 +6485,10 @@
         <v>317</v>
       </c>
       <c r="B317">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C317" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18941209447620891</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
@@ -6495,10 +6496,10 @@
         <v>318</v>
       </c>
       <c r="B318">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C318" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.18998420169365191</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
@@ -6506,10 +6507,10 @@
         <v>319</v>
       </c>
       <c r="B319">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C319" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.19055658409466644</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
@@ -6517,10 +6518,10 @@
         <v>320</v>
       </c>
       <c r="B320">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C320" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.19112924181161589</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
@@ -6528,10 +6529,10 @@
         <v>321</v>
       </c>
       <c r="B321">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C321" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.19170217497692718</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
@@ -6539,10 +6540,10 @@
         <v>322</v>
       </c>
       <c r="B322">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C322" s="2">
-        <v>0.10983549256377799</v>
+        <v>0.19227538372309097</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
@@ -6553,7 +6554,7 @@
         <v>-4.0129662380177468E-3</v>
       </c>
       <c r="C323" s="2">
-        <v>0.10538176020236577</v>
+        <v>0.18749082286179061</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
@@ -6564,7 +6565,7 @@
         <v>-3.609842547209511E-3</v>
       </c>
       <c r="C324" s="2">
-        <v>0.10139150609347794</v>
+        <v>0.18320416796500325</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
@@ -6575,7 +6576,7 @@
         <v>-1.04927462669504E-2</v>
       </c>
       <c r="C325" s="2">
-        <v>8.9834884479464708E-2</v>
+        <v>0.17078910684854834</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
@@ -6586,7 +6587,7 @@
         <v>2.2163589231951459E-2</v>
       </c>
       <c r="C326" s="2">
-        <v>0.11398953718971881</v>
+        <v>0.19673799568998276</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
@@ -6597,7 +6598,7 @@
         <v>1.7519069443272951E-2</v>
       </c>
       <c r="C327" s="2">
-        <v>0.13350559725082506</v>
+        <v>0.21770373174187896</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
@@ -6608,7 +6609,7 @@
         <v>-4.9628867679657178E-2</v>
       </c>
       <c r="C328" s="2">
-        <v>7.7250997950713163E-2</v>
+        <v>0.15727047436623651</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
@@ -6619,7 +6620,7 @@
         <v>3.2088281844695067E-2</v>
       </c>
       <c r="C329" s="2">
-        <v>0.11181813159043458</v>
+        <v>0.19440529551824426</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
@@ -6630,7 +6631,7 @@
         <v>3.5702225626614218E-4</v>
       </c>
       <c r="C330" s="2">
-        <v>0.11221507540833259</v>
+        <v>0.1948317247917464</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
@@ -6641,7 +6642,7 @@
         <v>1.7422180320905568E-2</v>
       </c>
       <c r="C331" s="2">
-        <v>0.13159228700772616</v>
+        <v>0.21564829855420684</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
@@ -6652,7 +6653,7 @@
         <v>1.9652482636792892E-2</v>
       </c>
       <c r="C332" s="2">
-        <v>0.15383088478007437</v>
+        <v>0.23953880563399024</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
@@ -6663,7 +6664,7 @@
         <v>2.3261701660259291E-2</v>
       </c>
       <c r="C333" s="2">
-        <v>0.18067095458822138</v>
+        <v>0.26837258752696214</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
@@ -6674,7 +6675,7 @@
         <v>8.0945926969956949E-2</v>
       </c>
       <c r="C334" s="2">
-        <v>0.27624145945386902</v>
+        <v>0.3710421823676151</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
@@ -6685,7 +6686,7 @@
         <v>-1.210397505119268E-2</v>
       </c>
       <c r="C335" s="2">
-        <v>0.26079386466934168</v>
+        <v>0.3544471219981048</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
@@ -6696,7 +6697,7 @@
         <v>5.3523500720303582E-2</v>
       </c>
       <c r="C336" s="2">
-        <v>0.32827596599312558</v>
+        <v>0.42694187350798357</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
@@ -6707,7 +6708,7 @@
         <v>-1.192106342957411E-2</v>
       </c>
       <c r="C337" s="2">
-        <v>0.31244150395054276</v>
+        <v>0.40993120892357948</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
@@ -6718,7 +6719,7 @@
         <v>-1.61130235830028E-4</v>
       </c>
       <c r="C338" s="2">
-        <v>0.31223002994149823</v>
+        <v>0.40970402637538172</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
@@ -6729,7 +6730,7 @@
         <v>2.549637970330448E-2</v>
       </c>
       <c r="C339" s="2">
-        <v>0.34568714504296538</v>
+        <v>0.44564637550112562</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
@@ -6740,7 +6741,7 @@
         <v>-1.929166704934587E-2</v>
       </c>
       <c r="C340" s="2">
-        <v>0.31972659668821168</v>
+        <v>0.41775744695386435</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
@@ -6751,7 +6752,7 @@
         <v>-1E-3</v>
       </c>
       <c r="C341" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.41633968950691042</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
@@ -6759,10 +6760,10 @@
         <v>342</v>
       </c>
       <c r="B342">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C342" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.41702094889756325</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
@@ -6770,10 +6771,10 @@
         <v>343</v>
       </c>
       <c r="B343">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C343" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.41770253597398294</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
@@ -6781,10 +6782,10 @@
         <v>344</v>
       </c>
       <c r="B344">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C344" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.4183844508937864</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
@@ -6792,10 +6793,10 @@
         <v>345</v>
       </c>
       <c r="B345">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C345" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.41906669381466627</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
@@ -6803,10 +6804,10 @@
         <v>346</v>
       </c>
       <c r="B346">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C346" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.41974926489439102</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
@@ -6814,10 +6815,10 @@
         <v>347</v>
       </c>
       <c r="B347">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C347" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42043216429080504</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
@@ -6825,10 +6826,10 @@
         <v>348</v>
       </c>
       <c r="B348">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C348" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42111539216182875</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
@@ -6836,10 +6837,10 @@
         <v>349</v>
       </c>
       <c r="B349">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C349" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42179894866545853</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
@@ -6847,10 +6848,10 @@
         <v>350</v>
       </c>
       <c r="B350">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C350" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42248283395976644</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
@@ -6858,10 +6859,10 @@
         <v>351</v>
       </c>
       <c r="B351">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C351" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42316704820290113</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
@@ -6869,10 +6870,10 @@
         <v>352</v>
       </c>
       <c r="B352">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C352" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42385159155308655</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
@@ -6880,10 +6881,10 @@
         <v>353</v>
       </c>
       <c r="B353">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C353" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.4245364641686234</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
@@ -6891,10 +6892,10 @@
         <v>354</v>
       </c>
       <c r="B354">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C354" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42522166620788854</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
@@ -6902,10 +6903,10 @@
         <v>355</v>
       </c>
       <c r="B355">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C355" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42590719782933434</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
@@ -6913,10 +6914,10 @@
         <v>356</v>
       </c>
       <c r="B356">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C356" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42659305919149004</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
@@ -6924,10 +6925,10 @@
         <v>357</v>
       </c>
       <c r="B357">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C357" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42727925045296106</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
@@ -6935,10 +6936,10 @@
         <v>358</v>
       </c>
       <c r="B358">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C358" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42796577177242878</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
@@ -6946,10 +6947,10 @@
         <v>359</v>
       </c>
       <c r="B359">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C359" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42865262330865134</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
@@ -6957,10 +6958,10 @@
         <v>360</v>
       </c>
       <c r="B360">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C360" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.42933980522046283</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
@@ -6968,10 +6969,10 @@
         <v>361</v>
       </c>
       <c r="B361">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C361" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.43002731766677388</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
@@ -6979,10 +6980,10 @@
         <v>362</v>
       </c>
       <c r="B362">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C362" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.43071516080657146</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
@@ -6990,10 +6991,10 @@
         <v>363</v>
       </c>
       <c r="B363">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C363" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.43140333479891951</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
@@ -7001,10 +7002,10 @@
         <v>364</v>
       </c>
       <c r="B364">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C364" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.43209183980295762</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
@@ -7012,10 +7013,10 @@
         <v>365</v>
       </c>
       <c r="B365">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C365" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.43278067597790282</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
@@ -7023,10 +7024,10 @@
         <v>366</v>
       </c>
       <c r="B366">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C366" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.43346984348304801</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
@@ -7034,10 +7035,10 @@
         <v>367</v>
       </c>
       <c r="B367">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C367" s="2">
-        <v>0.31840687009152335</v>
+        <v>0.43415934247776333</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
@@ -7048,7 +7049,7 @@
         <v>-2.1942810454221421E-2</v>
       </c>
       <c r="C368" s="2">
-        <v>0.28947731803956173</v>
+        <v>0.40268985586462291</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
@@ -7059,7 +7060,7 @@
         <v>3.5377688462121309E-3</v>
       </c>
       <c r="C369" s="2">
-        <v>0.29403919072321938</v>
+        <v>0.40765224833759872</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
@@ -7070,7 +7071,7 @@
         <v>-1.060892963563788E-2</v>
       </c>
       <c r="C370" s="2">
-        <v>0.28031082000307889</v>
+        <v>0.39271856468353777</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
@@ -7081,7 +7082,7 @@
         <v>-3.749734353000135E-3</v>
       </c>
       <c r="C371" s="2">
-        <v>0.27550999453879554</v>
+        <v>0.38749624003748268</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
@@ -7092,7 +7093,7 @@
         <v>-7.5208243063928731E-4</v>
       </c>
       <c r="C372" s="2">
-        <v>0.27455070588179808</v>
+        <v>0.38645272849277235</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
@@ -7103,7 +7104,7 @@
         <v>-7.8727543632161321E-4</v>
       </c>
       <c r="C373" s="2">
-        <v>0.27354728341871093</v>
+        <v>0.38536120831600895</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
@@ -7114,7 +7115,7 @@
         <v>-2.53478967026113E-3</v>
       </c>
       <c r="C374" s="2">
-        <v>0.27031910892011213</v>
+        <v>0.38184960903558901</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
@@ -7125,7 +7126,7 @@
         <v>-8.7957290976654076E-4</v>
       </c>
       <c r="C375" s="2">
-        <v>0.26920177064514716</v>
+        <v>0.38063417155410972</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
@@ -7136,7 +7137,7 @@
         <v>9.5266911898818146E-4</v>
       </c>
       <c r="C376" s="2">
-        <v>0.27041089997780604</v>
+        <v>0.38194945909396921</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
@@ -7147,7 +7148,7 @@
         <v>4.7715598434430037E-3</v>
       </c>
       <c r="C377" s="2">
-        <v>0.27647274161281243</v>
+        <v>0.38854351363864992</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
@@ -7158,7 +7159,7 @@
         <v>7.4797029961187426E-3</v>
       </c>
       <c r="C378" s="2">
-        <v>0.28602037860271762</v>
+        <v>0.39892940671785398</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
@@ -7169,7 +7170,7 @@
         <v>-2.2970394238526061E-3</v>
       </c>
       <c r="C379" s="2">
-        <v>0.28306633909318918</v>
+        <v>0.39571601071943635</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
@@ -7180,7 +7181,7 @@
         <v>-1.5094612762293211E-4</v>
       </c>
       <c r="C380" s="2">
-        <v>0.28287266519781978</v>
+        <v>0.39550533279235706</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
@@ -7191,7 +7192,7 @@
         <v>2.3815098098849279E-2</v>
       </c>
       <c r="C381" s="2">
-        <v>0.31342440356783813</v>
+        <v>0.4287394291902743</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
@@ -7202,7 +7203,7 @@
         <v>5.2323934294075183E-3</v>
       </c>
       <c r="C382" s="2">
-        <v>0.32029675678708996</v>
+        <v>0.43621515599190502</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
@@ -7213,7 +7214,7 @@
         <v>1.7356415240133299E-2</v>
       </c>
       <c r="C383" s="2">
-        <v>0.34321237553808798</v>
+        <v>0.46114270261347345</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
@@ -7224,7 +7225,7 @@
         <v>-1.0254677127714889E-2</v>
       </c>
       <c r="C384" s="2">
-        <v>0.329438166312994</v>
+        <v>0.44615915596065547</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
@@ -7235,7 +7236,7 @@
         <v>3.4125929691649752E-3</v>
       </c>
       <c r="C385" s="2">
-        <v>0.33397499765229355</v>
+        <v>0.45109430852858057</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
@@ -7246,7 +7247,7 @@
         <v>-1.4477014452213451E-2</v>
       </c>
       <c r="C386" s="2">
-        <v>0.31466302233238991</v>
+        <v>0.43008679525248766</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
@@ -7257,7 +7258,7 @@
         <v>1.6578197395916189E-3</v>
       </c>
       <c r="C387" s="2">
-        <v>0.3168424966417237</v>
+        <v>0.43245762137098637</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
@@ -7268,7 +7269,7 @@
         <v>-3.7743315869123032E-3</v>
       </c>
       <c r="C388" s="2">
-        <v>0.31187229641166025</v>
+        <v>0.42705105132373261</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
@@ -7279,7 +7280,7 @@
         <v>-7.5200635349733343E-3</v>
       </c>
       <c r="C389" s="2">
-        <v>0.3020069333928731</v>
+        <v>0.41631953675012767</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
@@ -7290,7 +7291,7 @@
         <v>5.2447144584117861E-3</v>
       </c>
       <c r="C390" s="2">
-        <v>0.30883558798139121</v>
+        <v>0.42374772830225227</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
@@ -7301,7 +7302,7 @@
         <v>9.8037029528900803E-3</v>
       </c>
       <c r="C391" s="2">
-        <v>0.32166702330013208</v>
+        <v>0.43770572811037967</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
@@ -7312,7 +7313,7 @@
         <v>-1.2920528219533369E-2</v>
       </c>
       <c r="C392" s="2">
-        <v>0.3045903872287562</v>
+        <v>0.41912981067894461</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
@@ -7323,7 +7324,7 @@
         <v>1.499409424548322E-3</v>
       </c>
       <c r="C393" s="2">
-        <v>0.3065465023505422</v>
+        <v>0.42125766729173419</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
@@ -7334,7 +7335,7 @@
         <v>2.449910119214533E-2</v>
       </c>
       <c r="C394" s="2">
-        <v>0.33855571732387174</v>
+        <v>0.45607720270282698</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
@@ -7345,7 +7346,7 @@
         <v>1.0714424867883911E-2</v>
       </c>
       <c r="C395" s="2">
-        <v>0.35289757198861482</v>
+        <v>0.47167823249302498</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
@@ -7356,7 +7357,7 @@
         <v>-1.8502841517442858E-2</v>
       </c>
       <c r="C396" s="2">
-        <v>0.3278651226247763</v>
+        <v>0.44444800339253621</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
@@ -7367,7 +7368,7 @@
         <v>2.678717746230476E-3</v>
       </c>
       <c r="C397" s="2">
-        <v>0.33142209849335158</v>
+        <v>0.44831727189273096</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
@@ -7378,7 +7379,7 @@
         <v>1.72804315756005E-2</v>
       </c>
       <c r="C398" s="2">
-        <v>0.35442964696460849</v>
+        <v>0.47334481940943363</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
@@ -7389,7 +7390,7 @@
         <v>-6.4651925339150786E-3</v>
       </c>
       <c r="C399" s="2">
-        <v>0.34567299852333977</v>
+        <v>0.46381936148310532</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
@@ -7400,7 +7401,7 @@
         <v>2.0948343779989439E-2</v>
       </c>
       <c r="C400" s="2">
-        <v>0.37386261911185587</v>
+        <v>0.49448395269925782</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
@@ -7411,7 +7412,7 @@
         <v>-9.6154818295968638E-3</v>
       </c>
       <c r="C401" s="2">
-        <v>0.36065226806142364</v>
+        <v>0.48011376940745409</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
@@ -7422,7 +7423,7 @@
         <v>-3.981930070295318E-3</v>
       </c>
       <c r="C402" s="2">
-        <v>0.35523424588001434</v>
+        <v>0.47422005988159244</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
@@ -7433,7 +7434,7 @@
         <v>3.438085799263016E-3</v>
       </c>
       <c r="C403" s="2">
-        <v>0.35989365749544933</v>
+        <v>0.4792885549344601</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
@@ -7444,7 +7445,7 @@
         <v>1.7183930640091501E-2</v>
       </c>
       <c r="C404" s="2">
-        <v>0.38326197578375171</v>
+        <v>0.50470854685913513</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
@@ -7455,7 +7456,7 @@
         <v>3.96245567579959E-3</v>
       </c>
       <c r="C405" s="2">
-        <v>0.38874309005081387</v>
+        <v>0.51067088778106129</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
@@ -7466,7 +7467,7 @@
         <v>-2.5000000000000001E-4</v>
       </c>
       <c r="C406" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51029322005911615</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
@@ -7474,10 +7475,10 @@
         <v>407</v>
       </c>
       <c r="B407">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C407" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51101967109796442</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
@@ -7485,10 +7486,10 @@
         <v>408</v>
       </c>
       <c r="B408">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C408" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51174647155976261</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
@@ -7496,10 +7497,10 @@
         <v>409</v>
       </c>
       <c r="B409">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C409" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51247362161258281</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
@@ -7507,10 +7508,10 @@
         <v>410</v>
       </c>
       <c r="B410">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C410" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51320112142457841</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
@@ -7518,10 +7519,10 @@
         <v>411</v>
       </c>
       <c r="B411">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C411" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51392897116398362</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
@@ -7529,10 +7530,10 @@
         <v>412</v>
       </c>
       <c r="B412">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C412" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51465717099911334</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
@@ -7540,10 +7541,10 @@
         <v>413</v>
       </c>
       <c r="B413">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C413" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51538572109836389</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
@@ -7551,10 +7552,10 @@
         <v>414</v>
       </c>
       <c r="B414">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C414" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51611462163021227</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
@@ -7562,10 +7563,10 @@
         <v>415</v>
       </c>
       <c r="B415">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C415" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51684387276321642</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
@@ -7573,10 +7574,10 @@
         <v>416</v>
       </c>
       <c r="B416">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C416" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51757347466601544</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
@@ -7584,10 +7585,10 @@
         <v>417</v>
       </c>
       <c r="B417">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C417" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51830342750732972</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
@@ -7595,10 +7596,10 @@
         <v>418</v>
       </c>
       <c r="B418">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C418" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51903373145596055</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
@@ -7606,10 +7607,10 @@
         <v>419</v>
       </c>
       <c r="B419">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C419" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.51976438668079084</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
@@ -7617,10 +7618,10 @@
         <v>420</v>
       </c>
       <c r="B420">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C420" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52049539335078432</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
@@ -7628,10 +7629,10 @@
         <v>421</v>
       </c>
       <c r="B421">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C421" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.521226751634986</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
@@ -7639,10 +7640,10 @@
         <v>422</v>
       </c>
       <c r="B422">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C422" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52195846170252225</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
@@ -7650,10 +7651,10 @@
         <v>423</v>
       </c>
       <c r="B423">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C423" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52269052372260116</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
@@ -7661,10 +7662,10 @@
         <v>424</v>
       </c>
       <c r="B424">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C424" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52342293786451166</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
@@ -7672,10 +7673,10 @@
         <v>425</v>
       </c>
       <c r="B425">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C425" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52415570429762459</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
@@ -7683,10 +7684,10 @@
         <v>426</v>
       </c>
       <c r="B426">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C426" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52488882319139152</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
@@ -7694,10 +7695,10 @@
         <v>427</v>
       </c>
       <c r="B427">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C427" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52562229471534638</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
@@ -7705,10 +7706,10 @@
         <v>428</v>
       </c>
       <c r="B428">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C428" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.5263561190391044</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
@@ -7716,10 +7717,10 @@
         <v>429</v>
       </c>
       <c r="B429">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C429" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52709029633236215</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
@@ -7727,10 +7728,10 @@
         <v>430</v>
       </c>
       <c r="B430">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C430" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52782482676489795</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
@@ -7738,10 +7739,10 @@
         <v>431</v>
       </c>
       <c r="B431">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C431" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52855971050657191</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
@@ -7749,10 +7750,10 @@
         <v>432</v>
       </c>
       <c r="B432">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C432" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.52929494772732544</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
@@ -7760,10 +7761,10 @@
         <v>433</v>
       </c>
       <c r="B433">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C433" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53003053859718219</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
@@ -7771,10 +7772,10 @@
         <v>434</v>
       </c>
       <c r="B434">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C434" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53076648328624743</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
@@ -7782,10 +7783,10 @@
         <v>435</v>
       </c>
       <c r="B435">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C435" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.5315027819647079</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
@@ -7793,10 +7794,10 @@
         <v>436</v>
       </c>
       <c r="B436">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C436" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53223943480283287</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
@@ -7804,10 +7805,10 @@
         <v>437</v>
       </c>
       <c r="B437">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C437" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53297644197097294</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
@@ -7815,10 +7816,10 @@
         <v>438</v>
       </c>
       <c r="B438">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C438" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53371380363956089</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
@@ -7826,10 +7827,10 @@
         <v>439</v>
       </c>
       <c r="B439">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C439" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53445151997911156</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
@@ -7837,10 +7838,10 @@
         <v>440</v>
       </c>
       <c r="B440">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C440" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53518959116022136</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
@@ -7848,10 +7849,10 @@
         <v>441</v>
       </c>
       <c r="B441">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C441" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53592801735356943</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
@@ -7859,10 +7860,10 @@
         <v>442</v>
       </c>
       <c r="B442">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C442" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53666679872991641</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
@@ -7870,10 +7871,10 @@
         <v>443</v>
       </c>
       <c r="B443">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C443" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53740593546010529</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
@@ -7881,10 +7882,10 @@
         <v>444</v>
       </c>
       <c r="B444">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C444" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53814542771506158</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
@@ -7892,10 +7893,10 @@
         <v>445</v>
       </c>
       <c r="B445">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C445" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53888527566579225</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
@@ -7903,10 +7904,10 @@
         <v>446</v>
       </c>
       <c r="B446">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C446" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.53962547948338735</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
@@ -7914,10 +7915,10 @@
         <v>447</v>
       </c>
       <c r="B447">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C447" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54036603933901883</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
@@ -7925,10 +7926,10 @@
         <v>448</v>
       </c>
       <c r="B448">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C448" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54110695540394094</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
@@ -7936,10 +7937,10 @@
         <v>449</v>
       </c>
       <c r="B449">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C449" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54184822784949005</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
@@ -7947,10 +7948,10 @@
         <v>450</v>
       </c>
       <c r="B450">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C450" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54258985684708561</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
@@ -7958,10 +7959,10 @@
         <v>451</v>
       </c>
       <c r="B451">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C451" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54333184256822908</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
@@ -7969,10 +7970,10 @@
         <v>452</v>
       </c>
       <c r="B452">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C452" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54407418518450446</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
@@ -7980,10 +7981,10 @@
         <v>453</v>
       </c>
       <c r="B453">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C453" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54481688486757807</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
@@ -7991,10 +7992,10 @@
         <v>454</v>
       </c>
       <c r="B454">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C454" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.5455599417891992</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
@@ -8002,10 +8003,10 @@
         <v>455</v>
       </c>
       <c r="B455">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C455" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54630335612119973</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
@@ -8013,10 +8014,10 @@
         <v>456</v>
       </c>
       <c r="B456">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C456" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54704712803549393</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.3">
@@ -8024,10 +8025,10 @@
         <v>457</v>
       </c>
       <c r="B457">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C457" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54779125770407888</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
@@ -8035,10 +8036,10 @@
         <v>458</v>
       </c>
       <c r="B458">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C458" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54853574529903459</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
@@ -8046,10 +8047,10 @@
         <v>459</v>
       </c>
       <c r="B459">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C459" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.54928059099252324</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
@@ -8057,10 +8058,10 @@
         <v>460</v>
       </c>
       <c r="B460">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C460" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55002579495679038</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
@@ -8068,10 +8069,10 @@
         <v>461</v>
       </c>
       <c r="B461">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C461" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.5507713573641646</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
@@ -8079,10 +8080,10 @@
         <v>462</v>
       </c>
       <c r="B462">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C462" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55151727838705678</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
@@ -8090,10 +8091,10 @@
         <v>463</v>
       </c>
       <c r="B463">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C463" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.5522635581979608</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
@@ -8101,10 +8102,10 @@
         <v>464</v>
       </c>
       <c r="B464">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C464" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55301019696945386</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
@@ -8112,10 +8113,10 @@
         <v>465</v>
       </c>
       <c r="B465">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C465" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55375719487419617</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
@@ -8123,10 +8124,10 @@
         <v>466</v>
       </c>
       <c r="B466">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C466" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55450455208493055</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
@@ -8134,10 +8135,10 @@
         <v>467</v>
       </c>
       <c r="B467">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C467" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55525226877448319</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
@@ -8145,10 +8146,10 @@
         <v>468</v>
       </c>
       <c r="B468">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C468" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55600034511576357</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
@@ -8156,10 +8157,10 @@
         <v>469</v>
       </c>
       <c r="B469">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C469" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55674878128176397</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
@@ -8167,10 +8168,10 @@
         <v>470</v>
       </c>
       <c r="B470">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C470" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55749757744556039</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.3">
@@ -8178,10 +8179,10 @@
         <v>471</v>
       </c>
       <c r="B471">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C471" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55824673378031153</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.3">
@@ -8189,10 +8190,10 @@
         <v>472</v>
       </c>
       <c r="B472">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C472" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55899625045925971</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.3">
@@ -8200,10 +8201,10 @@
         <v>473</v>
       </c>
       <c r="B473">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C473" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.55974612765573051</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
@@ -8211,10 +8212,10 @@
         <v>474</v>
       </c>
       <c r="B474">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C474" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56049636554313276</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
@@ -8222,10 +8223,10 @@
         <v>475</v>
       </c>
       <c r="B475">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C475" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56124696429495879</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
@@ -8233,10 +8234,10 @@
         <v>476</v>
       </c>
       <c r="B476">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C476" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56199792408478455</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
@@ -8244,10 +8245,10 @@
         <v>477</v>
       </c>
       <c r="B477">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C477" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56274924508626922</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
@@ -8255,10 +8256,10 @@
         <v>478</v>
       </c>
       <c r="B478">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C478" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56350092747315561</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
@@ -8266,10 +8267,10 @@
         <v>479</v>
       </c>
       <c r="B479">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C479" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56425297141927022</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.3">
@@ -8277,10 +8278,10 @@
         <v>480</v>
       </c>
       <c r="B480">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C480" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56500537709852272</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
@@ -8288,10 +8289,10 @@
         <v>481</v>
       </c>
       <c r="B481">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C481" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56575814468490704</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
@@ -8299,10 +8300,10 @@
         <v>482</v>
       </c>
       <c r="B482">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C482" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56651127435250037</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
@@ -8310,10 +8311,10 @@
         <v>483</v>
       </c>
       <c r="B483">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C483" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56726476627546385</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.3">
@@ -8321,10 +8322,10 @@
         <v>484</v>
       </c>
       <c r="B484">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C484" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.5680186206280422</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
@@ -8332,10 +8333,10 @@
         <v>485</v>
       </c>
       <c r="B485">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C485" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56877283758456432</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
@@ -8343,10 +8344,10 @@
         <v>486</v>
       </c>
       <c r="B486">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C486" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.56952741731944234</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
@@ -8354,10 +8355,10 @@
         <v>487</v>
       </c>
       <c r="B487">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C487" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.57028236000717303</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
@@ -8365,10 +8366,10 @@
         <v>488</v>
       </c>
       <c r="B488">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C488" s="2">
-        <v>0.38839590427830134</v>
+        <v>0.5710376658223365</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
@@ -8379,7 +8380,7 @@
         <v>-6.9770226122973763E-3</v>
       </c>
       <c r="C489" s="2">
-        <v>0.37870903465933053</v>
+        <v>0.56007650050312319</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
@@ -8390,7 +8391,7 @@
         <v>3.3598177125944502E-3</v>
       </c>
       <c r="C490" s="2">
-        <v>0.38334124569449302</v>
+        <v>0.56531807316251592</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
@@ -8401,7 +8402,7 @@
         <v>-1.1204537637742739E-2</v>
       </c>
       <c r="C491" s="2">
-        <v>0.367841546641267</v>
+        <v>0.54777940789672752</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
@@ -8412,7 +8413,7 @@
         <v>-2.3777204558888538E-3</v>
       </c>
       <c r="C492" s="2">
-        <v>0.3645892018154035</v>
+        <v>0.54409922113736797</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
@@ -8423,7 +8424,7 @@
         <v>4.2292522061923698E-3</v>
       </c>
       <c r="C493" s="2">
-        <v>0.37036039370772755</v>
+        <v>0.55062960617494328</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
@@ -8434,7 +8435,7 @@
         <v>-4.3254250044852359E-3</v>
       </c>
       <c r="C494" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.54392247410369921</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
@@ -8442,10 +8443,10 @@
         <v>495</v>
       </c>
       <c r="B495">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C495" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.54466510081374309</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
@@ -8453,10 +8454,10 @@
         <v>496</v>
       </c>
       <c r="B496">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C496" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.54540808472723457</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
@@ -8464,10 +8465,10 @@
         <v>497</v>
       </c>
       <c r="B497">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C497" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.54615142601598821</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
@@ -8475,10 +8476,10 @@
         <v>498</v>
       </c>
       <c r="B498">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C498" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.54689512485190195</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
@@ -8486,10 +8487,10 @@
         <v>499</v>
       </c>
       <c r="B499">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C499" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.54763918140695556</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
@@ -8497,10 +8498,10 @@
         <v>500</v>
       </c>
       <c r="B500">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C500" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.54838359585321228</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
@@ -8508,10 +8509,10 @@
         <v>501</v>
       </c>
       <c r="B501">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C501" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.54912836836281764</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
@@ -8519,10 +8520,10 @@
         <v>502</v>
       </c>
       <c r="B502">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C502" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.54987349910800021</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
@@ -8530,10 +8531,10 @@
         <v>503</v>
       </c>
       <c r="B503">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C503" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.55061898826107092</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
@@ -8541,10 +8542,10 @@
         <v>504</v>
       </c>
       <c r="B504">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C504" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.55136483599442443</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
@@ -8552,10 +8553,10 @@
         <v>505</v>
       </c>
       <c r="B505">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C505" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.55211104248053777</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
@@ -8563,10 +8564,10 @@
         <v>506</v>
       </c>
       <c r="B506">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C506" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.55285760789197069</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.3">
@@ -8574,10 +8575,10 @@
         <v>507</v>
       </c>
       <c r="B507">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C507" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.55360453240136676</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.3">
@@ -8585,10 +8586,10 @@
         <v>508</v>
       </c>
       <c r="B508">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C508" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.5543518161814518</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.3">
@@ -8596,10 +8597,10 @@
         <v>509</v>
       </c>
       <c r="B509">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C509" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.55509945940503513</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.3">
@@ -8607,10 +8608,10 @@
         <v>510</v>
       </c>
       <c r="B510">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C510" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.55584746224500892</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.3">
@@ -8618,10 +8619,10 @@
         <v>511</v>
       </c>
       <c r="B511">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C511" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.55659582487434878</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
@@ -8629,10 +8630,10 @@
         <v>512</v>
       </c>
       <c r="B512">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C512" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.55734454746611339</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
@@ -8640,10 +8641,10 @@
         <v>513</v>
       </c>
       <c r="B513">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C513" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.5580936301934446</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
@@ -8651,10 +8652,10 @@
         <v>514</v>
       </c>
       <c r="B514">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C514" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.55884307322956739</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
@@ -8662,10 +8663,10 @@
         <v>515</v>
       </c>
       <c r="B515">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C515" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.5595928767477909</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
@@ -8673,10 +8674,10 @@
         <v>516</v>
       </c>
       <c r="B516">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C516" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56034304092150644</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.3">
@@ -8684,10 +8685,10 @@
         <v>517</v>
       </c>
       <c r="B517">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C517" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.5610935659241898</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.3">
@@ -8695,10 +8696,10 @@
         <v>518</v>
       </c>
       <c r="B518">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C518" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56184445192939936</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
@@ -8706,10 +8707,10 @@
         <v>519</v>
       </c>
       <c r="B519">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C519" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56259569911077734</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.3">
@@ -8717,10 +8718,10 @@
         <v>520</v>
       </c>
       <c r="B520">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C520" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56334730764204943</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
@@ -8728,10 +8729,10 @@
         <v>521</v>
       </c>
       <c r="B521">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C521" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56409927769702539</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
@@ -8739,10 +8740,10 @@
         <v>522</v>
       </c>
       <c r="B522">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C522" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56485160944959745</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
@@ -8750,10 +8751,10 @@
         <v>523</v>
       </c>
       <c r="B523">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C523" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56560430307374276</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
@@ -8761,10 +8762,10 @@
         <v>524</v>
       </c>
       <c r="B524">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C524" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56635735874352122</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
@@ -8772,10 +8773,10 @@
         <v>525</v>
       </c>
       <c r="B525">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C525" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56711077663307696</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
@@ -8783,10 +8784,10 @@
         <v>526</v>
       </c>
       <c r="B526">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C526" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56786455691663751</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
@@ -8794,10 +8795,10 @@
         <v>527</v>
       </c>
       <c r="B527">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C527" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56861869976851442</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.3">
@@ -8805,10 +8806,10 @@
         <v>528</v>
       </c>
       <c r="B528">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C528" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.56937320536310299</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.3">
@@ -8816,10 +8817,10 @@
         <v>529</v>
       </c>
       <c r="B529">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C529" s="2">
-        <v>0.36443300259562789</v>
+        <v>0.57012807387488262</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.3">
@@ -8830,7 +8831,7 @@
         <v>-3.7168166814044641E-3</v>
       </c>
       <c r="C530" s="2">
-        <v>0.35936165525092179</v>
+        <v>0.56429219565796307</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.3">
@@ -8841,7 +8842,7 @@
         <v>4.8037214818385583E-4</v>
       </c>
       <c r="C531" s="2">
-        <v>0.36001465472941335</v>
+        <v>0.56504363806037849</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.3">
@@ -8852,7 +8853,7 @@
         <v>4.5060876585696569E-3</v>
       </c>
       <c r="C532" s="2">
-        <v>0.36614299998056338</v>
+        <v>0.57209586188296524</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.3">
@@ -8863,7 +8864,7 @@
         <v>-1.5053126973238881E-3</v>
       </c>
       <c r="C533" s="2">
-        <v>0.36408652757633236</v>
+        <v>0.5697293660206626</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.3">
@@ -8874,7 +8875,7 @@
         <v>-1.4732037820044169E-4</v>
       </c>
       <c r="C534" s="2">
-        <v>0.36388556983319176</v>
+        <v>0.5694981128967882</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.3">
@@ -8885,7 +8886,7 @@
         <v>-1.5198832202608821E-3</v>
       </c>
       <c r="C535" s="2">
-        <v>0.36181262304124628</v>
+        <v>0.56711265905076513</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.3">
@@ -8896,7 +8897,7 @@
         <v>-7.6328284547278564E-4</v>
       </c>
       <c r="C536" s="2">
-        <v>0.36077317482733062</v>
+        <v>0.56591650884118849</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.3">
@@ -8907,7 +8908,7 @@
         <v>-5.109454075554647E-5</v>
       </c>
       <c r="C537" s="2">
-        <v>0.36070364674689048</v>
+        <v>0.56583649905630784</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.3">
@@ -8918,7 +8919,7 @@
         <v>-2.5000000000000001E-4</v>
       </c>
       <c r="C538" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.5654450399315436</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.3">
@@ -8926,10 +8927,10 @@
         <v>539</v>
       </c>
       <c r="B539">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C539" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.56619801899575062</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.3">
@@ -8937,10 +8938,10 @@
         <v>540</v>
       </c>
       <c r="B540">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C540" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.56695136024288761</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.3">
@@ -8948,10 +8949,10 @@
         <v>541</v>
       </c>
       <c r="B541">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C541" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.56770506384716446</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.3">
@@ -8959,10 +8960,10 @@
         <v>542</v>
       </c>
       <c r="B542">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C542" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.56845912998287473</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.3">
@@ -8970,10 +8971,10 @@
         <v>543</v>
       </c>
       <c r="B543">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C543" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.5692135588243965</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.3">
@@ -8981,10 +8982,10 @@
         <v>544</v>
       </c>
       <c r="B544">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C544" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.5699683505461911</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.3">
@@ -8992,10 +8993,10 @@
         <v>545</v>
       </c>
       <c r="B545">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C545" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.5707235053228038</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.3">
@@ -9003,10 +9004,10 @@
         <v>546</v>
       </c>
       <c r="B546">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C546" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.57147902332886391</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.3">
@@ -9014,10 +9015,10 @@
         <v>547</v>
       </c>
       <c r="B547">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C547" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.572234904739085</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.3">
@@ -9025,10 +9026,10 @@
         <v>548</v>
       </c>
       <c r="B548">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C548" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.57299114972826426</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.3">
@@ -9036,10 +9037,10 @@
         <v>549</v>
       </c>
       <c r="B549">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C549" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.57374775847128345</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.3">
@@ -9047,10 +9048,10 @@
         <v>550</v>
       </c>
       <c r="B550">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C550" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.57450473114310796</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.3">
@@ -9058,10 +9059,10 @@
         <v>551</v>
       </c>
       <c r="B551">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C551" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.57526206791878765</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.3">
@@ -9069,10 +9070,10 @@
         <v>552</v>
       </c>
       <c r="B552">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C552" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.57601976897345653</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.3">
@@ -9080,10 +9081,10 @@
         <v>553</v>
       </c>
       <c r="B553">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C553" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.57677783448233266</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.3">
@@ -9091,10 +9092,10 @@
         <v>554</v>
       </c>
       <c r="B554">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C554" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.5775362646207185</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.3">
@@ -9102,10 +9103,10 @@
         <v>555</v>
       </c>
       <c r="B555">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C555" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.57829505956400107</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.3">
@@ -9113,10 +9114,10 @@
         <v>556</v>
       </c>
       <c r="B556">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C556" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.57905421948765134</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.3">
@@ -9124,10 +9125,10 @@
         <v>557</v>
       </c>
       <c r="B557">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C557" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.57981374456722479</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.3">
@@ -9135,10 +9136,10 @@
         <v>558</v>
       </c>
       <c r="B558">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C558" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.58057363497836145</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.3">
@@ -9146,10 +9147,10 @@
         <v>559</v>
       </c>
       <c r="B559">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C559" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.58133389089678589</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.3">
@@ -9157,10 +9158,10 @@
         <v>560</v>
       </c>
       <c r="B560">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C560" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.58209451249830724</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.3">
@@ -9168,10 +9169,10 @@
         <v>561</v>
       </c>
       <c r="B561">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C561" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.58285549995881891</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.3">
@@ -9179,10 +9180,10 @@
         <v>562</v>
       </c>
       <c r="B562">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C562" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.58361685345429914</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.3">
@@ -9190,10 +9191,10 @@
         <v>563</v>
       </c>
       <c r="B563">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C563" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.58437857316081054</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.3">
@@ -9201,10 +9202,10 @@
         <v>564</v>
       </c>
       <c r="B564">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C564" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.58514065925450065</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
@@ -9212,10 +9213,10 @@
         <v>565</v>
       </c>
       <c r="B565">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C565" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.58590311191160194</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.3">
@@ -9223,10 +9224,10 @@
         <v>566</v>
       </c>
       <c r="B566">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C566" s="2">
-        <v>0.36036347083520381</v>
+        <v>0.58666593130843125</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.3">
@@ -9237,7 +9238,7 @@
         <v>-3.5791801311307711E-3</v>
       </c>
       <c r="C567" s="2">
-        <v>0.35549448492927438</v>
+        <v>0.58098696813234996</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.3">
@@ -9248,7 +9249,7 @@
         <v>-5.7464498370020812E-4</v>
       </c>
       <c r="C568" s="2">
-        <v>0.35471555682307637</v>
+        <v>0.58007846190181733</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.3">
@@ -9259,7 +9260,7 @@
         <v>6.8165728016806714E-3</v>
       </c>
       <c r="C569" s="2">
-        <v>0.36395007404173013</v>
+        <v>0.59084918176973877</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.3">
@@ -9270,7 +9271,7 @@
         <v>-7.6466447352707689E-5</v>
       </c>
       <c r="C570" s="2">
-        <v>0.36384577762520165</v>
+        <v>0.5907275351845348</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.3">
@@ -9281,7 +9282,7 @@
         <v>-7.9235360661952759E-5</v>
       </c>
       <c r="C571" s="2">
-        <v>0.36373771281312428</v>
+        <v>0.59060149331456957</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.3">
@@ -9292,7 +9293,7 @@
         <v>-2.5094156257631402E-3</v>
       </c>
       <c r="C572" s="2">
-        <v>0.36031552808714851</v>
+        <v>0.58661001307288385</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.3">
@@ -9303,7 +9304,7 @@
         <v>3.6484138730909308E-4</v>
       </c>
       <c r="C573" s="2">
-        <v>0.36081182749159413</v>
+        <v>0.58718887407117193</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.3">
@@ -9314,7 +9315,7 @@
         <v>1.1517463293610371E-3</v>
       </c>
       <c r="C574" s="2">
-        <v>0.36237913751885886</v>
+        <v>0.58901691303088621</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.3">
@@ -9325,7 +9326,7 @@
         <v>-1.4910722487182959E-4</v>
       </c>
       <c r="C575" s="2">
-        <v>0.36217599694644009</v>
+        <v>0.58877997912870994</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.3">
@@ -9336,7 +9337,7 @@
         <v>-3.5757995198077049E-3</v>
       </c>
       <c r="C576" s="2">
-        <v>0.35730512867066549</v>
+        <v>0.58309882044226158</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.3">
@@ -9347,7 +9348,7 @@
         <v>1.409114636144538E-3</v>
       </c>
       <c r="C577" s="2">
-        <v>0.3592177271931894</v>
+        <v>0.58532958816060987</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.3">
@@ -9358,7 +9359,7 @@
         <v>-4.4347917199462922E-3</v>
       </c>
       <c r="C578" s="2">
-        <v>0.35318987967102883</v>
+        <v>0.57829898162964921</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
@@ -9369,7 +9370,7 @@
         <v>-5.2372742413807159E-3</v>
       </c>
       <c r="C579" s="2">
-        <v>0.34610285317053069</v>
+        <v>0.57003299702796284</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.3">
@@ -9380,7 +9381,7 @@
         <v>2.0842395655152092E-3</v>
       </c>
       <c r="C580" s="2">
-        <v>0.34890845399636161</v>
+        <v>0.57330532191953298</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.3">
@@ -9391,7 +9392,7 @@
         <v>2.9872438654724282E-3</v>
       </c>
       <c r="C581" s="2">
-        <v>0.35293797250064612</v>
+        <v>0.57800516859095208</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.3">
@@ -9402,7 +9403,7 @@
         <v>-2.3638726760288201E-3</v>
       </c>
       <c r="C582" s="2">
-        <v>0.34973979939509009</v>
+        <v>0.57427496529028788</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.3">
@@ -9413,7 +9414,7 @@
         <v>-2.2248116337036791E-3</v>
       </c>
       <c r="C583" s="2">
-        <v>0.34673688258692292</v>
+        <v>0.57077250003286162</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.3">
@@ -9424,7 +9425,7 @@
         <v>-1.622396015279551E-3</v>
       </c>
       <c r="C584" s="2">
-        <v>0.34455194203498396</v>
+        <v>0.56822408498789767</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.3">
@@ -9435,7 +9436,7 @@
         <v>-7.1850755854823472E-5</v>
       </c>
       <c r="C585" s="2">
-        <v>0.34445533496166264</v>
+        <v>0.56811140690204154</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.3">
@@ -9446,7 +9447,7 @@
         <v>-3.9079725271244569E-3</v>
       </c>
       <c r="C586" s="2">
-        <v>0.3392012404486866</v>
+        <v>0.5619832706043979</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.3">
@@ -9457,7 +9458,7 @@
         <v>2.986606878059008E-3</v>
       </c>
       <c r="C587" s="2">
-        <v>0.34320090808451598</v>
+        <v>0.56664830058379834</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
@@ -9468,7 +9469,7 @@
         <v>-2.5000000000000001E-4</v>
       </c>
       <c r="C588" s="2">
-        <v>0.34286510785749497</v>
+        <v>0.56625663850865238</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.3">
@@ -9479,7 +9480,7 @@
         <v>-2.7544871743773601E-3</v>
       </c>
       <c r="C589" s="2">
-        <v>0.33916620314098284</v>
+        <v>0.56194240468609702</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
@@ -9490,7 +9491,7 @@
         <v>-1.3003131543258971E-3</v>
       </c>
       <c r="C590" s="2">
-        <v>0.33742486771121011</v>
+        <v>0.55991139043098426</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
@@ -9501,7 +9502,7 @@
         <v>-1.040198217557374E-3</v>
       </c>
       <c r="C591" s="2">
-        <v>0.33603368074770001</v>
+        <v>0.55828877338311056</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.3">
@@ -9512,7 +9513,7 @@
         <v>9.6928665204482484E-3</v>
       </c>
       <c r="C592" s="2">
-        <v>0.34898367688201065</v>
+        <v>0.57339305846382616</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.3">
@@ -9523,7 +9524,7 @@
         <v>-4.682501723740619E-3</v>
       </c>
       <c r="C593" s="2">
-        <v>0.34266705848971268</v>
+        <v>0.56602564275544776</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
@@ -9534,7 +9535,7 @@
         <v>5.9255386048861049E-3</v>
       </c>
       <c r="C594" s="2">
-        <v>0.35062308397830239</v>
+        <v>0.57530518815783693</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
@@ -9545,7 +9546,7 @@
         <v>-1.077275172177144E-3</v>
       </c>
       <c r="C595" s="2">
-        <v>0.34916809126296328</v>
+        <v>0.57360815099003271</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
@@ -9556,7 +9557,7 @@
         <v>4.3406639661396941E-6</v>
       </c>
       <c r="C596" s="2">
-        <v>0.34917394754828107</v>
+        <v>0.57361498149423051</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
@@ -9567,7 +9568,7 @@
         <v>-8.8593779478131005E-5</v>
       </c>
       <c r="C597" s="2">
-        <v>0.34905441912909424</v>
+        <v>0.57347556899557672</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
@@ -9578,7 +9579,7 @@
         <v>-7.2816652027776546E-4</v>
       </c>
       <c r="C598" s="2">
-        <v>0.3480720828670516</v>
+        <v>0.57232981676575923</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
@@ -9589,7 +9590,7 @@
         <v>-3.2255447240620151E-3</v>
       </c>
       <c r="C599" s="2">
-        <v>0.34372381607250446</v>
+        <v>0.56725819662080512</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.3">
@@ -9600,7 +9601,7 @@
         <v>3.062191491473E-3</v>
       </c>
       <c r="C600" s="2">
-        <v>0.34783855570897143</v>
+        <v>0.57205744133543879</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.3">
@@ -9611,7 +9612,7 @@
         <v>-4.7323998321550402E-3</v>
       </c>
       <c r="C601" s="2">
-        <v>0.3414600447541622</v>
+        <v>0.56461783696392498</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
@@ -9622,7 +9623,7 @@
         <v>-3.9913367392742788E-3</v>
       </c>
       <c r="C602" s="2">
-        <v>0.33610582599326622</v>
+        <v>0.55837292030832686</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.3">
@@ -9633,7 +9634,7 @@
         <v>5.0636584637971885E-7</v>
       </c>
       <c r="C603" s="2">
-        <v>0.33610650255162366</v>
+        <v>0.55837370941514963</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.3">
@@ -9644,7 +9645,7 @@
         <v>4.0850057217080649E-3</v>
       </c>
       <c r="C604" s="2">
-        <v>0.34156450525935839</v>
+        <v>0.56473967493467003</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
@@ -9655,7 +9656,7 @@
         <v>8.028743187423075E-3</v>
       </c>
       <c r="C605" s="2">
-        <v>0.35233558214144806</v>
+        <v>0.57730256793989243</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.3">
@@ -9666,7 +9667,7 @@
         <v>-6.2001340888507422E-3</v>
       </c>
       <c r="C606" s="2">
-        <v>0.34395092019904694</v>
+        <v>0.56752308051997635</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.3">
@@ -9677,7 +9678,7 @@
         <v>8.1664699305236173E-3</v>
       </c>
       <c r="C607" s="2">
-        <v>0.35492625497695229</v>
+        <v>0.58032421062244455</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
@@ -9688,7 +9689,7 @@
         <v>7.0257666491295966E-4</v>
       </c>
       <c r="C608" s="2">
-        <v>0.35587819454637698</v>
+        <v>0.58143450953582487</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.3">
@@ -9699,7 +9700,7 @@
         <v>4.330117854922432E-3</v>
       </c>
       <c r="C609" s="2">
-        <v>0.36174930692568208</v>
+        <v>0.58828230734195641</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
@@ -9710,7 +9711,7 @@
         <v>-1.824853499289399E-2</v>
       </c>
       <c r="C610" s="2">
-        <v>0.3368993770466997</v>
+        <v>0.55929848207783239</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.3">
@@ -9721,7 +9722,7 @@
         <v>-8.2869211182868309E-3</v>
       </c>
       <c r="C611" s="2">
-        <v>0.32582059736602675</v>
+        <v>0.546376698556989</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.3">
@@ -9732,7 +9733,7 @@
         <v>-3.3844965262439688E-3</v>
       </c>
       <c r="C612" s="2">
-        <v>0.32133336215981873</v>
+        <v>0.5411429919924583</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
@@ -9743,7 +9744,7 @@
         <v>1.851424993060764E-3</v>
       </c>
       <c r="C613" s="2">
-        <v>0.32377971177068643</v>
+        <v>0.54399630264571353</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
@@ -9754,7 +9755,7 @@
         <v>-3.408411282298969E-3</v>
       </c>
       <c r="C614" s="2">
-        <v>0.31926772606580867</v>
+        <v>0.53873372822794807</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.3">
@@ -9765,7 +9766,7 @@
         <v>-8.7840772512045868E-4</v>
       </c>
       <c r="C615" s="2">
-        <v>0.31810887110373043</v>
+        <v>0.53738209263416903</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
@@ -9776,7 +9777,7 @@
         <v>9.5913984915889806E-4</v>
       </c>
       <c r="C616" s="2">
-        <v>0.3193731218475358</v>
+        <v>0.53885665706259767</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.3">
@@ -9787,7 +9788,7 @@
         <v>-1.2096839944871681E-2</v>
       </c>
       <c r="C617" s="2">
-        <v>0.30341287636498038</v>
+        <v>0.5202413543840112</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.3">
@@ -9798,7 +9799,7 @@
         <v>-2.9642065663093068E-3</v>
       </c>
       <c r="C618" s="2">
-        <v>0.29954929135824726</v>
+        <v>0.51573504497897116</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
@@ -9809,7 +9810,7 @@
         <v>-2.9101296430311331E-3</v>
       </c>
       <c r="C619" s="2">
-        <v>0.29576743444288556</v>
+        <v>0.51132405949359683</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
@@ -9820,7 +9821,7 @@
         <v>-4.5262387816284262E-3</v>
       </c>
       <c r="C620" s="2">
-        <v>0.28990248162913901</v>
+        <v>0.50448344592390892</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
@@ -9831,7 +9832,7 @@
         <v>-2.6905922351700721E-3</v>
       </c>
       <c r="C621" s="2">
-        <v>0.2864318800279409</v>
+        <v>0.50043549444636426</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
@@ -9842,7 +9843,7 @@
         <v>3.0184266391152718E-3</v>
       </c>
       <c r="C622" s="2">
-        <v>0.29031488028402436</v>
+        <v>0.50496444891307535</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.3">
@@ -9853,7 +9854,7 @@
         <v>2.3402283696159938E-3</v>
       </c>
       <c r="C623" s="2">
-        <v>0.29333451177260256</v>
+        <v>0.50848640941168499</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.3">
@@ -9864,7 +9865,7 @@
         <v>3.9881819383590809E-3</v>
       </c>
       <c r="C624" s="2">
-        <v>0.2984925651127105</v>
+        <v>0.51450252766396087</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.3">
@@ -9875,7 +9876,7 @@
         <v>3.1236056504552628E-3</v>
       </c>
       <c r="C625" s="2">
-        <v>0.3025485438261708</v>
+        <v>0.51923323631700102</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.3">
@@ -9886,7 +9887,7 @@
         <v>3.9728450333117874E-3</v>
       </c>
       <c r="C626" s="2">
-        <v>0.30772336733915834</v>
+        <v>0.52526891453434532</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.3">
@@ -9897,7 +9898,7 @@
         <v>2.4397590842535782E-3</v>
       </c>
       <c r="C627" s="2">
-        <v>0.31091389730431473</v>
+        <v>0.52899020322451007</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.3">
@@ -9908,7 +9909,7 @@
         <v>-6.4556619082925884E-5</v>
       </c>
       <c r="C628" s="2">
-        <v>0.31082926913519598</v>
+        <v>0.52889149678637892</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.3">
@@ -9919,7 +9920,7 @@
         <v>-5.1478872312688776E-3</v>
       </c>
       <c r="C629" s="2">
-        <v>0.3040812678782413</v>
+        <v>0.52102093577207687</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.3">
@@ -9930,7 +9931,7 @@
         <v>2.4731616817092491E-3</v>
       </c>
       <c r="C630" s="2">
-        <v>0.3073064716997928</v>
+        <v>0.52478266646750593</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.3">
@@ -9941,7 +9942,7 @@
         <v>2.252360720902684E-3</v>
       </c>
       <c r="C631" s="2">
-        <v>0.31025099744683132</v>
+        <v>0.52821702705337059</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.3">
@@ -9952,7 +9953,7 @@
         <v>-1.9566181835661809E-4</v>
       </c>
       <c r="C632" s="2">
-        <v>0.30999463135416733</v>
+        <v>0.52791801333101374</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.3">
@@ -9963,7 +9964,7 @@
         <v>-1.1776123729366581E-3</v>
       </c>
       <c r="C633" s="2">
-        <v>0.30845196546780412</v>
+        <v>0.52611871817368239</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.3">
@@ -9974,7 +9975,7 @@
         <v>1.6756073305317009E-4</v>
       </c>
       <c r="C634" s="2">
-        <v>0.30867121063830266</v>
+        <v>0.52637443574482579</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.3">
@@ -9985,7 +9986,7 @@
         <v>2.3749818232459878E-3</v>
       </c>
       <c r="C635" s="2">
-        <v>0.3117792809761738</v>
+        <v>0.52999954728518706</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.3">
@@ -9996,7 +9997,7 @@
         <v>-2.1067903100789472E-3</v>
       </c>
       <c r="C636" s="2">
-        <v>0.30901563709805091</v>
+        <v>0.52677615906454123</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
@@ -10007,7 +10008,7 @@
         <v>-1.0682386964545279E-3</v>
       </c>
       <c r="C637" s="2">
-        <v>0.30761729594023879</v>
+        <v>0.5251451976906043</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.3">
@@ -10018,7 +10019,7 @@
         <v>1.9787870570101649E-3</v>
       </c>
       <c r="C638" s="2">
-        <v>0.31020479212096802</v>
+        <v>0.52816313526785597</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.3">
@@ -10029,7 +10030,7 @@
         <v>3.35238091319652E-3</v>
       </c>
       <c r="C639" s="2">
-        <v>0.31459709765845306</v>
+        <v>0.5332861201947785</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.3">
@@ -10040,7 +10041,7 @@
         <v>-2.2163958504518209E-3</v>
       </c>
       <c r="C640" s="2">
-        <v>0.31168343010618682</v>
+        <v>0.52988775120042331</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.3">
@@ -10051,7 +10052,7 @@
         <v>2.8383921836353269E-3</v>
       </c>
       <c r="C641" s="2">
-        <v>0.31540650210160409</v>
+        <v>0.53423017263526984</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.3">
@@ -10062,7 +10063,7 @@
         <v>-1.142107994418123E-3</v>
       </c>
       <c r="C642" s="2">
-        <v>0.31390416581964414</v>
+        <v>0.53247791608982564</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.3">
@@ -10073,7 +10074,7 @@
         <v>-3.0049722361851622E-4</v>
       </c>
       <c r="C643" s="2">
-        <v>0.31350934126571472</v>
+        <v>0.53201741073078412</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.3">
@@ -10084,7 +10085,7 @@
         <v>-1.714360929214301E-3</v>
       </c>
       <c r="C644" s="2">
-        <v>0.31125751217089087</v>
+        <v>0.52939097993895134</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.3">
@@ -10095,7 +10096,7 @@
         <v>-2.1599875091208912E-3</v>
       </c>
       <c r="C645" s="2">
-        <v>0.30842521232336084</v>
+        <v>0.52608751452572111</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.3">
@@ -10106,7 +10107,7 @@
         <v>7.3475941158219326E-3</v>
       </c>
       <c r="C646" s="2">
-        <v>0.31803898971442096</v>
+        <v>0.53730058616767939</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
@@ -10117,7 +10118,7 @@
         <v>-1.9457618817056599E-3</v>
       </c>
       <c r="C647" s="2">
-        <v>0.31547439968963259</v>
+        <v>0.5343093652863905</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
@@ -10128,7 +10129,7 @@
         <v>-1.969421143371048E-3</v>
       </c>
       <c r="C648" s="2">
-        <v>0.31288367659332039</v>
+        <v>0.5312876639819234</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.3">
@@ -10139,7 +10140,7 @@
         <v>-1.6666666666666669E-4</v>
       </c>
       <c r="C649" s="2">
-        <v>0.31266486264722149</v>
+        <v>0.5310324493712596</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.3">
@@ -10147,10 +10148,10 @@
         <v>650</v>
       </c>
       <c r="B650">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C650" s="2">
-        <v>0.31266486264722149</v>
+        <v>0.53176887597940725</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.3">
@@ -10161,7 +10162,7 @@
         <v>-4.0324800168837077E-3</v>
       </c>
       <c r="C651" s="2">
-        <v>0.30737156781973113</v>
+        <v>0.52559204859653585</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.3">
@@ -10172,7 +10173,7 @@
         <v>3.6604348156621462E-4</v>
       </c>
       <c r="C652" s="2">
-        <v>0.30785012266011647</v>
+        <v>0.52615048162145395</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.3">
@@ -10183,7 +10184,7 @@
         <v>3.728091580886037E-3</v>
       </c>
       <c r="C653" s="2">
-        <v>0.3127259076914663</v>
+        <v>0.53184011038315193</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.3">
@@ -10194,7 +10195,7 @@
         <v>8.8733989160396185E-3</v>
       </c>
       <c r="C654" s="2">
-        <v>0.32437424833783296</v>
+        <v>0.54543273875817189</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.3">
@@ -10205,7 +10206,7 @@
         <v>-2.470947905030876E-3</v>
       </c>
       <c r="C655" s="2">
-        <v>0.32110178856342569</v>
+        <v>0.54161405496997128</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.3">
@@ -10216,7 +10217,7 @@
         <v>-1.1662163401912509E-3</v>
       </c>
       <c r="C656" s="2">
-        <v>0.31956109807054728</v>
+        <v>0.539816199468797</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.3">
@@ -10227,7 +10228,7 @@
         <v>5.0003089705207568E-3</v>
       </c>
       <c r="C657" s="2">
-        <v>0.32615931126637976</v>
+        <v>0.54751575622395421</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.3">
@@ -10238,7 +10239,7 @@
         <v>-1.8611304237846191E-3</v>
       </c>
       <c r="C658" s="2">
-        <v>0.32369115582539648</v>
+        <v>0.54463562756875972</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.3">
@@ -10246,10 +10247,10 @@
         <v>659</v>
       </c>
       <c r="B659">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C659" s="2">
-        <v>0.32369115582539648</v>
+        <v>0.54537859730562022</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.3">
@@ -10260,7 +10261,7 @@
         <v>1.277223484572386E-4</v>
       </c>
       <c r="C660" s="2">
-        <v>0.3238602207684505</v>
+        <v>0.54557597668932378</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.3">
@@ -10271,7 +10272,7 @@
         <v>-4.0738240277297319E-3</v>
       </c>
       <c r="C661" s="2">
-        <v>0.31846704719172836</v>
+        <v>0.53927957213880484</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.3">
@@ -10282,7 +10283,7 @@
         <v>1.191945323772462E-3</v>
       </c>
       <c r="C662" s="2">
-        <v>0.32003858782317679</v>
+        <v>0.54111430922679427</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.3">
@@ -10293,7 +10294,7 @@
         <v>6.7216473952945194E-4</v>
       </c>
       <c r="C663" s="2">
-        <v>0.32092587121672977</v>
+        <v>0.54215019192504055</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.3">
@@ -10304,7 +10305,7 @@
         <v>-2.3742354579918889E-3</v>
       </c>
       <c r="C664" s="2">
-        <v>0.31778968217590831</v>
+        <v>0.53848876425782322</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.3">
@@ -10315,7 +10316,7 @@
         <v>6.5664112855783269E-4</v>
       </c>
       <c r="C665" s="2">
-        <v>0.3186549970800141</v>
+        <v>0.53949899925625888</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.3">
@@ -10326,7 +10327,7 @@
         <v>-1.1905526559935859E-2</v>
       </c>
       <c r="C666" s="2">
-        <v>0.3029557149888859</v>
+        <v>0.52117045303161891</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.3">
@@ -10337,7 +10338,7 @@
         <v>8.4507016345483268E-3</v>
       </c>
       <c r="C667" s="2">
-        <v>0.31396660497928652</v>
+        <v>0.53402541066547971</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.3">
@@ -10348,7 +10349,7 @@
         <v>-1.622296776016183E-3</v>
       </c>
       <c r="C668" s="2">
-        <v>0.31183496119223575</v>
+        <v>0.53153676618743018</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.3">
@@ -10359,7 +10360,7 @@
         <v>7.7712932774076128E-3</v>
       </c>
       <c r="C669" s="2">
-        <v>0.32202961540721731</v>
+        <v>0.54343878756260522</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.3">
@@ -10370,7 +10371,7 @@
         <v>2.1341743322020449E-3</v>
       </c>
       <c r="C670" s="2">
-        <v>0.32485105707883039</v>
+        <v>0.54673275500634644</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.3">
@@ -10381,7 +10382,7 @@
         <v>-7.1106732558637474E-3</v>
       </c>
       <c r="C671" s="2">
-        <v>0.31543047409925717</v>
+        <v>0.53573444377135448</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.3">
@@ -10392,7 +10393,7 @@
         <v>4.2757210174237193E-3</v>
       </c>
       <c r="C672" s="2">
-        <v>0.32105488782432301</v>
+        <v>0.5423008158097693</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.3">
@@ -10403,7 +10404,7 @@
         <v>-1.156101837379974E-2</v>
       </c>
       <c r="C673" s="2">
-        <v>0.3057821479933881</v>
+        <v>0.52447024774026629</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.3">
@@ -10414,7 +10415,7 @@
         <v>-5.7609003987772972E-4</v>
       </c>
       <c r="C674" s="2">
-        <v>0.30502989990367896</v>
+        <v>0.52359201561445334</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.3">
@@ -10425,7 +10426,7 @@
         <v>-1.098982739147335E-4</v>
       </c>
       <c r="C675" s="2">
-        <v>0.30488647937027252</v>
+        <v>0.52342457548178711</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.3">
@@ -10436,7 +10437,7 @@
         <v>1.959038409748616E-2</v>
       </c>
       <c r="C676" s="2">
-        <v>0.33044970670475265</v>
+        <v>0.55326904805902533</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.3">
@@ -10447,7 +10448,7 @@
         <v>6.696998377464348E-3</v>
       </c>
       <c r="C677" s="2">
-        <v>0.33935972623185223</v>
+        <v>0.56367128835364211</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.3">
@@ -10458,7 +10459,7 @@
         <v>8.6166056837832343E-3</v>
       </c>
       <c r="C678" s="2">
-        <v>0.35090046086153193</v>
+        <v>0.57714482726443894</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.3">
@@ -10469,7 +10470,7 @@
         <v>-3.6440731782888028E-3</v>
       </c>
       <c r="C679" s="2">
-        <v>0.34597768072556845</v>
+        <v>0.5713975961011275</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.3">
@@ -10480,7 +10481,7 @@
         <v>-5.2177092936485153E-3</v>
       </c>
       <c r="C680" s="2">
-        <v>0.33895476047180323</v>
+        <v>0.56319850025993357</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.3">
@@ -10491,7 +10492,7 @@
         <v>-1.1683709901442331E-3</v>
       </c>
       <c r="C681" s="2">
-        <v>0.3373903645725525</v>
+        <v>0.56137210448039299</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.3">
@@ -10502,7 +10503,7 @@
         <v>1.116124162013179E-2</v>
       </c>
       <c r="C682" s="2">
-        <v>0.35231730157198315</v>
+        <v>0.57879895579743246</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.3">
@@ -10513,7 +10514,7 @@
         <v>6.8189886985529392E-3</v>
       </c>
       <c r="C683" s="2">
-        <v>0.36153873796826019</v>
+        <v>0.58956476803430236</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.3">
@@ -10524,7 +10525,7 @@
         <v>-8.2485992448200693E-3</v>
       </c>
       <c r="C684" s="2">
-        <v>0.35030795056246206</v>
+        <v>0.57645308528910222</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.3">
@@ -10535,7 +10536,7 @@
         <v>-3.636745129624845E-3</v>
       </c>
       <c r="C685" s="2">
-        <v>0.34539722469976025</v>
+        <v>0.57071992720909492</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.3">
@@ -10546,7 +10547,7 @@
         <v>-1.8985519483172592E-2</v>
       </c>
       <c r="C686" s="2">
-        <v>0.31985415947761653</v>
+        <v>0.54089899342845915</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.3">
@@ -10557,7 +10558,7 @@
         <v>2.8657682961279591E-2</v>
       </c>
       <c r="C687" s="2">
-        <v>0.35767812153505246</v>
+        <v>0.58505758825748699</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.3">
@@ -10568,7 +10569,7 @@
         <v>1.409356202227534E-3</v>
       </c>
       <c r="C688" s="2">
-        <v>0.35959157361626637</v>
+        <v>0.58729149900038546</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.3">
@@ -10579,7 +10580,7 @@
         <v>9.4238544898066681E-3</v>
       </c>
       <c r="C689" s="2">
-        <v>0.37240416677159344</v>
+        <v>0.60224990311987225</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.3">
@@ -10590,7 +10591,7 @@
         <v>1.3449358865463459E-2</v>
       </c>
       <c r="C690" s="2">
-        <v>0.39086212291896172</v>
+        <v>0.62379913705908541</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.3">
@@ -10601,7 +10602,7 @@
         <v>-4.6915983983683237E-4</v>
       </c>
       <c r="C691" s="2">
-        <v>0.39020958626813779</v>
+        <v>0.62303731571601562</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.3">
@@ -10612,7 +10613,7 @@
         <v>1.6916021234497391E-3</v>
       </c>
       <c r="C692" s="2">
-        <v>0.39256126775630917</v>
+        <v>0.62578284908571868</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.3">
@@ -10623,7 +10624,7 @@
         <v>4.6365002952526574E-3</v>
       </c>
       <c r="C693" s="2">
-        <v>0.39901787848541859</v>
+        <v>0.63332079174552147</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.3">
@@ -10634,7 +10635,7 @@
         <v>2.6435142334127019E-3</v>
       </c>
       <c r="C694" s="2">
-        <v>0.40271620215999349</v>
+        <v>0.63763849850622956</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.3">
@@ -10645,7 +10646,7 @@
         <v>7.4691957529675378E-3</v>
       </c>
       <c r="C695" s="2">
-        <v>0.41319336405978563</v>
+        <v>0.64987034102416852</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.3">
@@ -10656,7 +10657,7 @@
         <v>1.1077358655089631E-2</v>
       </c>
       <c r="C696" s="2">
-        <v>0.42884781380246861</v>
+        <v>0.66814654652608818</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.3">
@@ -10667,7 +10668,7 @@
         <v>-4.9763896975216441E-3</v>
       </c>
       <c r="C697" s="2">
-        <v>0.42173731026253564</v>
+        <v>0.65984519923799956</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.3">
@@ -10678,7 +10679,7 @@
         <v>2.2480459740949728E-3</v>
       </c>
       <c r="C698" s="2">
-        <v>0.42493344109909204</v>
+        <v>0.66357660755576742</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.3">
@@ -10689,7 +10690,7 @@
         <v>-1.071858286473364E-2</v>
       </c>
       <c r="C699" s="2">
-        <v>0.40966017393394139</v>
+        <v>0.64574542383584854</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.3">
@@ -10700,7 +10701,7 @@
         <v>1.2771284696060901E-2</v>
       </c>
       <c r="C700" s="2">
-        <v>0.42766334533995037</v>
+        <v>0.66676370718089539</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.3">
@@ -10711,7 +10712,7 @@
         <v>-3.0634367238198839E-3</v>
       </c>
       <c r="C701" s="2">
-        <v>0.42328978901858449</v>
+        <v>0.66165768203038733</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.3">
@@ -10722,7 +10723,7 @@
         <v>-5.5217227333802044E-3</v>
       </c>
       <c r="C702" s="2">
-        <v>0.41543077743437268</v>
+        <v>0.65248246903242435</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.3">
@@ -10733,7 +10734,7 @@
         <v>4.1806025785595382E-3</v>
       </c>
       <c r="C703" s="2">
-        <v>0.42134813099228752</v>
+        <v>0.65939084150348581</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.3">
@@ -10744,7 +10745,7 @@
         <v>-4.5878966184373328E-3</v>
       </c>
       <c r="C704" s="2">
-        <v>0.41482713270848592</v>
+        <v>0.65177772787308608</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.3">
@@ -10755,7 +10756,7 @@
         <v>9.3051078630086697E-3</v>
       </c>
       <c r="C705" s="2">
-        <v>0.42799225178584976</v>
+        <v>0.66714769779666061</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.3">
@@ -10766,7 +10767,7 @@
         <v>-3.9572374237101708E-3</v>
       </c>
       <c r="C706" s="2">
-        <v>0.42234134740631474</v>
+        <v>0.66055039853608744</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.3">
@@ -10777,7 +10778,7 @@
         <v>2.9602927672164239E-3</v>
       </c>
       <c r="C707" s="2">
-        <v>0.42655189420955453</v>
+        <v>0.66546611387047194</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.3">
@@ -10788,7 +10789,7 @@
         <v>3.4949800501943972E-3</v>
       </c>
       <c r="C708" s="2">
-        <v>0.4315376646203839</v>
+        <v>0.67128688471272402</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.3">
@@ -10799,7 +10800,7 @@
         <v>7.5568711881677927E-3</v>
       </c>
       <c r="C709" s="2">
-        <v>0.44235561035293047</v>
+        <v>0.68391658441897218</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.3">
@@ -10810,7 +10811,7 @@
         <v>1.947461905359534E-3</v>
       </c>
       <c r="C710" s="2">
-        <v>0.44516454295807423</v>
+        <v>0.68719594781893112</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.3">
@@ -10821,7 +10822,7 @@
         <v>1.37866692142931E-3</v>
       </c>
       <c r="C711" s="2">
-        <v>0.44715694350947305</v>
+        <v>0.68952202906215865</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.3">
@@ -10832,7 +10833,7 @@
         <v>2.7090781150094129E-4</v>
       </c>
       <c r="C712" s="2">
-        <v>0.44754898962993733</v>
+        <v>0.6899797337775343</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.3">
@@ -10843,7 +10844,7 @@
         <v>-7.2749910409804419E-3</v>
       </c>
       <c r="C713" s="2">
-        <v>0.43701808369899936</v>
+        <v>0.6776851463548641</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.3">
@@ -10854,7 +10855,7 @@
         <v>1.4004646875023629E-3</v>
       </c>
       <c r="C714" s="2">
-        <v>0.43903057678052221</v>
+        <v>0.68003468515908139</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.3">
@@ -10865,7 +10866,7 @@
         <v>1.514941713962723E-3</v>
       </c>
       <c r="C715" s="2">
-        <v>0.44121062422895507</v>
+        <v>0.68257983978453329</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.3">
@@ -10876,7 +10877,7 @@
         <v>-1.7114285738534761E-3</v>
       </c>
       <c r="C716" s="2">
-        <v>0.43874409518570845</v>
+        <v>0.6797002245689362</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.3">
@@ -10887,7 +10888,7 @@
         <v>3.8264133155651511E-3</v>
       </c>
       <c r="C717" s="2">
-        <v>0.44424932474921774</v>
+        <v>0.68612745187438462</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.3">
@@ -10898,7 +10899,7 @@
         <v>6.7034434338892153E-3</v>
       </c>
       <c r="C718" s="2">
-        <v>0.45393076840210683</v>
+        <v>0.69743031187035254</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.3">
@@ -10909,7 +10910,7 @@
         <v>7.126824766463642E-3</v>
       </c>
       <c r="C719" s="2">
-        <v>0.46429267821107828</v>
+        <v>0.7095276002563361</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.3">
@@ -10920,7 +10921,7 @@
         <v>-5.7196999271287461E-3</v>
       </c>
       <c r="C720" s="2">
-        <v>0.45591736348621936</v>
+        <v>0.69974961536572555</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.3">
@@ -10931,7 +10932,7 @@
         <v>6.5803649274700548E-3</v>
       </c>
       <c r="C721" s="2">
-        <v>0.46549783104219872</v>
+        <v>0.71093458812015886</v>
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.3">
@@ -10942,7 +10943,7 @@
         <v>1.8941663316993939E-3</v>
       </c>
       <c r="C722" s="2">
-        <v>0.46827372769293729</v>
+        <v>0.71417538281271586</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.3">
@@ -10953,7 +10954,7 @@
         <v>-4.1095856961983366E-3</v>
       </c>
       <c r="C723" s="2">
-        <v>0.46223973098350657</v>
+        <v>0.70713083217873329</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.3">
@@ -10964,7 +10965,7 @@
         <v>8.2699766239846019E-3</v>
       </c>
       <c r="C724" s="2">
-        <v>0.47433241937740178</v>
+        <v>0.72124876425493478</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.3">
@@ -10975,7 +10976,7 @@
         <v>1.194912336876016E-2</v>
       </c>
       <c r="C725" s="2">
-        <v>0.491949399343105</v>
+        <v>0.74181617808734301</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.3">
@@ -10986,7 +10987,7 @@
         <v>-5.8897441887384126E-3</v>
       </c>
       <c r="C726" s="2">
-        <v>0.48316219903843205</v>
+        <v>0.73155732637460258</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.3">
@@ -10997,7 +10998,7 @@
         <v>8.1863366819582058E-3</v>
       </c>
       <c r="C727" s="2">
-        <v>0.49530386415371397</v>
+        <v>0.74573243763241637</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.3">
@@ -11008,7 +11009,7 @@
         <v>7.8399031316551959E-3</v>
       </c>
       <c r="C728" s="2">
-        <v>0.50702690160106867</v>
+        <v>0.75941881083724272</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.3">
@@ -11019,7 +11020,7 @@
         <v>-3.4847670428390508E-4</v>
       </c>
       <c r="C729" s="2">
-        <v>0.50650173783313135</v>
+        <v>0.75880569436858702</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.3">
@@ -11030,7 +11031,7 @@
         <v>-1.652618647822571E-3</v>
       </c>
       <c r="C730" s="2">
-        <v>0.50401206496821116</v>
+        <v>0.75589905928017687</v>
       </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.3">
@@ -11041,7 +11042,7 @@
         <v>-1.264006807822924E-2</v>
       </c>
       <c r="C731" s="2">
-        <v>0.48500125007653483</v>
+        <v>0.73370437563237656</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.3">
@@ -11052,7 +11053,7 @@
         <v>5.6952463008581573E-4</v>
       </c>
       <c r="C732" s="2">
-        <v>0.48584699486416155</v>
+        <v>0.7346917629755868</v>
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.3">
@@ -11063,7 +11064,7 @@
         <v>-2.8927306942322008E-3</v>
       </c>
       <c r="C733" s="2">
-        <v>0.48154883965518536</v>
+        <v>0.7296737668677955</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.3">
@@ -11074,7 +11075,7 @@
         <v>6.0547881330127199E-3</v>
       </c>
       <c r="C734" s="2">
-        <v>0.49051930398800836</v>
+        <v>0.74014657506540971</v>
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.3">
@@ -11085,7 +11086,7 @@
         <v>-6.1031874562867397E-3</v>
       </c>
       <c r="C735" s="2">
-        <v>0.48142238526855552</v>
+        <v>0.72952613431637015</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.3">
@@ -11096,7 +11097,7 @@
         <v>5.1399213122938582E-5</v>
       </c>
       <c r="C736" s="2">
-        <v>0.48149852921346109</v>
+        <v>0.72961503059874988</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.3">
@@ -11107,7 +11108,7 @@
         <v>2.084828242770198E-3</v>
       </c>
       <c r="C737" s="2">
-        <v>0.48458719918878784</v>
+        <v>0.73322098086366194</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.3">
@@ -11118,7 +11119,7 @@
         <v>1.240767209268861E-3</v>
       </c>
       <c r="C738" s="2">
-        <v>0.48642922630484181</v>
+        <v>0.73537150462313461</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.3">
@@ -11129,7 +11130,7 @@
         <v>-1.1073751947383401E-2</v>
       </c>
       <c r="C739" s="2">
-        <v>0.46996887776540092</v>
+        <v>0.7161544310443807</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.3">
@@ -11140,7 +11141,7 @@
         <v>1.900524766599842E-3</v>
       </c>
       <c r="C740" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.71941602504389035</v>
       </c>
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.3">
@@ -11148,10 +11149,10 @@
         <v>741</v>
       </c>
       <c r="B741">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C741" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72024306415193651</v>
       </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.3">
@@ -11159,10 +11160,10 @@
         <v>742</v>
       </c>
       <c r="B742">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C742" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72107050106579351</v>
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.3">
@@ -11170,10 +11171,10 @@
         <v>743</v>
       </c>
       <c r="B743">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C743" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72189833597680608</v>
       </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.3">
@@ -11181,10 +11182,10 @@
         <v>744</v>
       </c>
       <c r="B744">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C744" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72272656907641075</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.3">
@@ -11192,10 +11193,10 @@
         <v>745</v>
       </c>
       <c r="B745">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C745" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72355520055613654</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.3">
@@ -11203,10 +11204,10 @@
         <v>746</v>
       </c>
       <c r="B746">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C746" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72438423060760382</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.3">
@@ -11214,10 +11215,10 @@
         <v>747</v>
       </c>
       <c r="B747">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C747" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72521365942252602</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.3">
@@ -11225,10 +11226,10 @@
         <v>748</v>
       </c>
       <c r="B748">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C748" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72604348719270806</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.3">
@@ -11236,10 +11237,10 @@
         <v>749</v>
       </c>
       <c r="B749">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C749" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72687371411004764</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.3">
@@ -11247,10 +11248,10 @@
         <v>750</v>
       </c>
       <c r="B750">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C750" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72770434036653453</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.3">
@@ -11258,10 +11259,10 @@
         <v>751</v>
       </c>
       <c r="B751">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C751" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72853536615425074</v>
       </c>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.3">
@@ -11269,10 +11270,10 @@
         <v>752</v>
       </c>
       <c r="B752">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C752" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.72936679166537088</v>
       </c>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.3">
@@ -11280,10 +11281,10 @@
         <v>753</v>
       </c>
       <c r="B753">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C753" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73019861709216172</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.3">
@@ -11291,10 +11292,10 @@
         <v>754</v>
       </c>
       <c r="B754">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C754" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73103084262698304</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.3">
@@ -11302,10 +11303,10 @@
         <v>755</v>
       </c>
       <c r="B755">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C755" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73186346846228645</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.3">
@@ -11313,10 +11314,10 @@
         <v>756</v>
       </c>
       <c r="B756">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C756" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73269649479061683</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.3">
@@ -11324,10 +11325,10 @@
         <v>757</v>
       </c>
       <c r="B757">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C757" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73352992180461118</v>
       </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.3">
@@ -11335,10 +11336,10 @@
         <v>758</v>
       </c>
       <c r="B758">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C758" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73436374969699902</v>
       </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.3">
@@ -11346,10 +11347,10 @@
         <v>759</v>
       </c>
       <c r="B759">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C759" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.7351979786606031</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.3">
@@ -11357,10 +11358,10 @@
         <v>760</v>
       </c>
       <c r="B760">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C760" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73603260888833888</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.3">
@@ -11368,10 +11369,10 @@
         <v>761</v>
       </c>
       <c r="B761">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C761" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73686764057321397</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.3">
@@ -11379,10 +11380,10 @@
         <v>762</v>
       </c>
       <c r="B762">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C762" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73770307390832957</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.3">
@@ -11390,10 +11391,10 @@
         <v>763</v>
       </c>
       <c r="B763">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C763" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73853890908687925</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.3">
@@ -11401,10 +11402,10 @@
         <v>764</v>
       </c>
       <c r="B764">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C764" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.73937514630214995</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.3">
@@ -11412,10 +11413,10 @@
         <v>765</v>
       </c>
       <c r="B765">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C765" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74021178574752122</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.3">
@@ -11423,10 +11424,10 @@
         <v>766</v>
       </c>
       <c r="B766">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C766" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74104882761646562</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.3">
@@ -11434,10 +11435,10 @@
         <v>767</v>
       </c>
       <c r="B767">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C767" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74188627210254909</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.3">
@@ -11445,10 +11446,10 @@
         <v>768</v>
       </c>
       <c r="B768">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C768" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74272411939943028</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.3">
@@ -11456,10 +11457,10 @@
         <v>769</v>
       </c>
       <c r="B769">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C769" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74356236970086143</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.3">
@@ -11467,10 +11468,10 @@
         <v>770</v>
       </c>
       <c r="B770">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C770" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74440102320068746</v>
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.3">
@@ -11478,10 +11479,10 @@
         <v>771</v>
       </c>
       <c r="B771">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C771" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74524008009284703</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.3">
@@ -11489,10 +11490,10 @@
         <v>772</v>
       </c>
       <c r="B772">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C772" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.7460795405713716</v>
       </c>
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.3">
@@ -11500,10 +11501,10 @@
         <v>773</v>
       </c>
       <c r="B773">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C773" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74691940483038655</v>
       </c>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.3">
@@ -11511,10 +11512,10 @@
         <v>774</v>
       </c>
       <c r="B774">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C774" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74775967306410995</v>
       </c>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.3">
@@ -11522,10 +11523,10 @@
         <v>775</v>
       </c>
       <c r="B775">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C775" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74860034546685372</v>
       </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.3">
@@ -11533,10 +11534,10 @@
         <v>776</v>
       </c>
       <c r="B776">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C776" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.74944142223302324</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.3">
@@ -11544,10 +11545,10 @@
         <v>777</v>
       </c>
       <c r="B777">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C777" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75028290355711735</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.3">
@@ -11555,10 +11556,10 @@
         <v>778</v>
       </c>
       <c r="B778">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C778" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75112478963372808</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.3">
@@ -11566,10 +11567,10 @@
         <v>779</v>
       </c>
       <c r="B779">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C779" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75196708065754192</v>
       </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.3">
@@ -11577,10 +11578,10 @@
         <v>780</v>
       </c>
       <c r="B780">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C780" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75280977682333827</v>
       </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.3">
@@ -11588,10 +11589,10 @@
         <v>781</v>
       </c>
       <c r="B781">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C781" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75365287832599026</v>
       </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.3">
@@ -11599,10 +11600,10 @@
         <v>782</v>
       </c>
       <c r="B782">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C782" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75449638536046504</v>
       </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.3">
@@ -11610,10 +11611,10 @@
         <v>783</v>
       </c>
       <c r="B783">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C783" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75534029812182324</v>
       </c>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.3">
@@ -11621,10 +11622,10 @@
         <v>784</v>
       </c>
       <c r="B784">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C784" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75618461680521987</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.3">
@@ -11632,10 +11633,10 @@
         <v>785</v>
       </c>
       <c r="B785">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C785" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75702934160590307</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.3">
@@ -11643,10 +11644,10 @@
         <v>786</v>
       </c>
       <c r="B786">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C786" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75787447271921538</v>
       </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.3">
@@ -11654,10 +11655,10 @@
         <v>787</v>
       </c>
       <c r="B787">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C787" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75872001034059311</v>
       </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.3">
@@ -11665,10 +11666,10 @@
         <v>788</v>
       </c>
       <c r="B788">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C788" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.75956595466556676</v>
       </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.3">
@@ -11676,10 +11677,10 @@
         <v>789</v>
       </c>
       <c r="B789">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C789" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.76041230588976072</v>
       </c>
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.3">
@@ -11687,10 +11688,10 @@
         <v>790</v>
       </c>
       <c r="B790">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C790" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.76125906420889378</v>
       </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.3">
@@ -11698,10 +11699,10 @@
         <v>791</v>
       </c>
       <c r="B791">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C791" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.76210622981877807</v>
       </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.3">
@@ -11709,10 +11710,10 @@
         <v>792</v>
       </c>
       <c r="B792">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C792" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.76295380291532067</v>
       </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.3">
@@ -11720,10 +11721,10 @@
         <v>793</v>
       </c>
       <c r="B793">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C793" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.76380178369452301</v>
       </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.3">
@@ -11731,10 +11732,10 @@
         <v>794</v>
       </c>
       <c r="B794">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C794" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.7646501723524799</v>
       </c>
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.3">
@@ -11742,10 +11743,10 @@
         <v>795</v>
       </c>
       <c r="B795">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C795" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.76549896908538129</v>
       </c>
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.3">
@@ -11753,10 +11754,10 @@
         <v>796</v>
       </c>
       <c r="B796">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C796" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.76634817408951139</v>
       </c>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.3">
@@ -11764,10 +11765,10 @@
         <v>797</v>
       </c>
       <c r="B797">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C797" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.76719778756124835</v>
       </c>
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.3">
@@ -11775,10 +11776,10 @@
         <v>798</v>
       </c>
       <c r="B798">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C798" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.7680478096970651</v>
       </c>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.3">
@@ -11786,10 +11787,10 @@
         <v>799</v>
       </c>
       <c r="B799">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C799" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.7688982406935293</v>
       </c>
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.3">
@@ -11797,10 +11798,10 @@
         <v>800</v>
       </c>
       <c r="B800">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C800" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.76974908074730275</v>
       </c>
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.3">
@@ -11808,10 +11809,10 @@
         <v>801</v>
       </c>
       <c r="B801">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C801" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77060033005514217</v>
       </c>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.3">
@@ -11819,10 +11820,10 @@
         <v>802</v>
       </c>
       <c r="B802">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C802" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77145198881389865</v>
       </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.3">
@@ -11830,10 +11831,10 @@
         <v>803</v>
       </c>
       <c r="B803">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C803" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77230405722051809</v>
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.3">
@@ -11841,10 +11842,10 @@
         <v>804</v>
       </c>
       <c r="B804">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C804" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77315653547204111</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.3">
@@ -11852,10 +11853,10 @@
         <v>805</v>
       </c>
       <c r="B805">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C805" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.774009423765603</v>
       </c>
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.3">
@@ -11863,10 +11864,10 @@
         <v>806</v>
       </c>
       <c r="B806">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C806" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77486272229843423</v>
       </c>
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.3">
@@ -11874,10 +11875,10 @@
         <v>807</v>
       </c>
       <c r="B807">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C807" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77571643126785972</v>
       </c>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.3">
@@ -11885,10 +11886,10 @@
         <v>808</v>
       </c>
       <c r="B808">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C808" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77657055087129945</v>
       </c>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.3">
@@ -11896,10 +11897,10 @@
         <v>809</v>
       </c>
       <c r="B809">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C809" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77742508130626842</v>
       </c>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.3">
@@ -11907,10 +11908,10 @@
         <v>810</v>
       </c>
       <c r="B810">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C810" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77828002277037656</v>
       </c>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.3">
@@ -11918,10 +11919,10 @@
         <v>811</v>
       </c>
       <c r="B811">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C811" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77913537546132916</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.3">
@@ -11929,10 +11930,10 @@
         <v>812</v>
       </c>
       <c r="B812">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C812" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.77999113957692601</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.3">
@@ -11940,10 +11941,10 @@
         <v>813</v>
       </c>
       <c r="B813">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C813" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78084731531506235</v>
       </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.3">
@@ -11951,10 +11952,10 @@
         <v>814</v>
       </c>
       <c r="B814">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C814" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78170390287372893</v>
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.3">
@@ -11962,10 +11963,10 @@
         <v>815</v>
       </c>
       <c r="B815">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C815" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78256090245101118</v>
       </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.3">
@@ -11973,10 +11974,10 @@
         <v>816</v>
       </c>
       <c r="B816">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C816" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78341831424509001</v>
       </c>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.3">
@@ -11984,10 +11985,10 @@
         <v>817</v>
       </c>
       <c r="B817">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C817" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78427613845424193</v>
       </c>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.3">
@@ -11995,10 +11996,10 @@
         <v>818</v>
       </c>
       <c r="B818">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C818" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78513437527683838</v>
       </c>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.3">
@@ -12006,10 +12007,10 @@
         <v>819</v>
       </c>
       <c r="B819">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C819" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78599302491134637</v>
       </c>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.3">
@@ -12017,10 +12018,10 @@
         <v>820</v>
       </c>
       <c r="B820">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C820" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78685208755632852</v>
       </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.3">
@@ -12028,10 +12029,10 @@
         <v>821</v>
       </c>
       <c r="B821">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C821" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78771156341044302</v>
       </c>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.3">
@@ -12039,10 +12040,10 @@
         <v>822</v>
       </c>
       <c r="B822">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C822" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78857145267244333</v>
       </c>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.3">
@@ -12050,10 +12051,10 @@
         <v>823</v>
       </c>
       <c r="B823">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C823" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.78943175554117861</v>
       </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.3">
@@ -12061,10 +12062,10 @@
         <v>824</v>
       </c>
       <c r="B824">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C824" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79029247221559384</v>
       </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.3">
@@ -12072,10 +12073,10 @@
         <v>825</v>
       </c>
       <c r="B825">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C825" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79115360289472958</v>
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.3">
@@ -12083,10 +12084,10 @@
         <v>826</v>
       </c>
       <c r="B826">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C826" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79201514777772186</v>
       </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.3">
@@ -12094,10 +12095,10 @@
         <v>827</v>
       </c>
       <c r="B827">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C827" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79287710706380299</v>
       </c>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.3">
@@ -12105,10 +12106,10 @@
         <v>828</v>
       </c>
       <c r="B828">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C828" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79373948095230051</v>
       </c>
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.3">
@@ -12116,10 +12117,10 @@
         <v>829</v>
       </c>
       <c r="B829">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C829" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79460226964263858</v>
       </c>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.3">
@@ -12127,10 +12128,10 @@
         <v>830</v>
       </c>
       <c r="B830">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C830" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.7954654733343367</v>
       </c>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.3">
@@ -12138,10 +12139,10 @@
         <v>831</v>
       </c>
       <c r="B831">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C831" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79632909222701043</v>
       </c>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.3">
@@ -12149,10 +12150,10 @@
         <v>832</v>
       </c>
       <c r="B832">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C832" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79719312652037155</v>
       </c>
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.3">
@@ -12160,10 +12161,10 @@
         <v>833</v>
       </c>
       <c r="B833">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C833" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79805757641422792</v>
       </c>
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.3">
@@ -12171,10 +12172,10 @@
         <v>834</v>
       </c>
       <c r="B834">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C834" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79892244210848307</v>
       </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.3">
@@ -12182,10 +12183,10 @@
         <v>835</v>
       </c>
       <c r="B835">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C835" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.79978772380313701</v>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.3">
@@ -12193,10 +12194,10 @@
         <v>836</v>
       </c>
       <c r="B836">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C836" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.80065342169828624</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.3">
@@ -12204,10 +12205,10 @@
         <v>837</v>
       </c>
       <c r="B837">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C837" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.80151953599412307</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.3">
@@ -12215,10 +12216,10 @@
         <v>838</v>
       </c>
       <c r="B838">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C838" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.80238606689093617</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.3">
@@ -12226,10 +12227,10 @@
         <v>839</v>
       </c>
       <c r="B839">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C839" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.80325301458911069</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.3">
@@ -12237,10 +12238,10 @@
         <v>840</v>
       </c>
       <c r="B840">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C840" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.80412037928912805</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.3">
@@ -12248,10 +12249,10 @@
         <v>841</v>
       </c>
       <c r="B841">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C841" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.80498816119156602</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.3">
@@ -12259,10 +12260,10 @@
         <v>842</v>
       </c>
       <c r="B842">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C842" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.80585636049709908</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.3">
@@ -12270,10 +12271,10 @@
         <v>843</v>
       </c>
       <c r="B843">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C843" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.80672497740649818</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.3">
@@ -12281,10 +12282,10 @@
         <v>844</v>
       </c>
       <c r="B844">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C844" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.80759401212063064</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.3">
@@ -12292,10 +12293,10 @@
         <v>845</v>
       </c>
       <c r="B845">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C845" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.8084634648404605</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.3">
@@ -12303,10 +12304,10 @@
         <v>846</v>
       </c>
       <c r="B846">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C846" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.8093333357670488</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.3">
@@ -12314,10 +12315,10 @@
         <v>847</v>
       </c>
       <c r="B847">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C847" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81020362510155275</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.3">
@@ -12325,10 +12326,10 @@
         <v>848</v>
       </c>
       <c r="B848">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C848" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81107433304522658</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.3">
@@ -12336,10 +12337,10 @@
         <v>849</v>
       </c>
       <c r="B849">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C849" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81194545979942123</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.3">
@@ -12347,10 +12348,10 @@
         <v>850</v>
       </c>
       <c r="B850">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C850" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81281700556558467</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.3">
@@ -12358,10 +12359,10 @@
         <v>851</v>
       </c>
       <c r="B851">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C851" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81368897054526168</v>
       </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.3">
@@ -12369,10 +12370,10 @@
         <v>852</v>
       </c>
       <c r="B852">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C852" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81456135494009407</v>
       </c>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.3">
@@ -12380,10 +12381,10 @@
         <v>853</v>
       </c>
       <c r="B853">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C853" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81543415895182025</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.3">
@@ -12391,10 +12392,10 @@
         <v>854</v>
       </c>
       <c r="B854">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C854" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81630738278227599</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.3">
@@ -12402,10 +12403,10 @@
         <v>855</v>
       </c>
       <c r="B855">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C855" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81718102663339409</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.3">
@@ -12413,10 +12414,10 @@
         <v>856</v>
       </c>
       <c r="B856">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C856" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81805509070720461</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.3">
@@ -12424,10 +12425,10 @@
         <v>857</v>
       </c>
       <c r="B857">
-        <v>0</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="C857" s="2">
-        <v>0.47276259002372484</v>
+        <v>0.81892957520583476</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.3">
@@ -12438,7 +12439,7 @@
         <v>-3.5075954829737271E-2</v>
       </c>
       <c r="C858" s="2">
-        <v>0.421104035941126</v>
+        <v>0.7551288835874419</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.3">
@@ -12449,7 +12450,7 @@
         <v>-5.3938233638943608E-2</v>
       </c>
       <c r="C859" s="2">
-        <v>0.34445219442528779</v>
+        <v>0.6604603317980442</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.3">
@@ -12460,7 +12461,7 @@
         <v>4.0963872258517393E-2</v>
       </c>
       <c r="C860" s="2">
-        <v>0.39952616237540894</v>
+        <v>0.72847921672015503</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.3">
@@ -12471,7 +12472,7 @@
         <v>-4.3239814362545396E-3</v>
       </c>
       <c r="C861" s="2">
-        <v>0.39347463722974507</v>
+        <v>0.72100530467410517</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.3">
@@ -12482,7 +12483,7 @@
         <v>2.0788293428826932E-2</v>
       </c>
       <c r="C862" s="2">
-        <v>0.42244259687410535</v>
+        <v>0.7567820679402385</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.3">
@@ -12493,7 +12494,7 @@
         <v>-4.5421360785837833E-2</v>
       </c>
       <c r="C863" s="2">
-        <v>0.35783331848434247</v>
+        <v>0.67698663581023477</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.3">
@@ -12504,7 +12505,7 @@
         <v>5.9519307089083498E-3</v>
       </c>
       <c r="C864" s="2">
-        <v>0.36591504831020844</v>
+        <v>0.68696794406634265</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.3">
@@ -12515,7 +12516,7 @@
         <v>5.1282305143987017E-3</v>
       </c>
       <c r="C865" s="2">
-        <v>0.37291977554102912</v>
+        <v>0.69561910455391629</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.3">
@@ -12526,7 +12527,7 @@
         <v>1.338519610483151E-2</v>
       </c>
       <c r="C866" s="2">
-        <v>0.39129657597284706</v>
+        <v>0.71831529878746925</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.3">
@@ -12537,7 +12538,7 @@
         <v>3.0466802035423689E-2</v>
       </c>
       <c r="C867" s="2">
-        <v>0.43368493332557478</v>
+        <v>0.77066687083006713</v>
       </c>
     </row>
   </sheetData>
